--- a/artfynd/A 39826-2020 artfynd.xlsx
+++ b/artfynd/A 39826-2020 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122335205</v>
+        <v>122335149</v>
       </c>
       <c r="B2" t="n">
-        <v>78808</v>
+        <v>78381</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,37 +687,29 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1249</v>
+        <v>6446</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Norsk näverlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Platismatia norvegica</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
@@ -726,10 +718,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>480539</v>
+        <v>480442</v>
       </c>
       <c r="R2" t="n">
-        <v>6596612</v>
+        <v>6596485</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -762,11 +754,6 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-01-26</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Endast en bål på lodyta</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -794,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122335213</v>
+        <v>122335180</v>
       </c>
       <c r="B3" t="n">
-        <v>78734</v>
+        <v>56584</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -810,26 +797,43 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6450</v>
+        <v>100138</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Skuggblåslav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hypogymnia vittata</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Parrique</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>stationär</t>
+        </is>
+      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -837,10 +841,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>480554</v>
+        <v>480403</v>
       </c>
       <c r="R3" t="n">
-        <v>6596596</v>
+        <v>6596616</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -881,7 +885,6 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -1006,10 +1009,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122335149</v>
+        <v>122335205</v>
       </c>
       <c r="B5" t="n">
-        <v>78381</v>
+        <v>78808</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1018,29 +1021,37 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6446</v>
+        <v>1249</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Norsk näverlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Platismatia norvegica</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
+          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="K5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
@@ -1049,10 +1060,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>480442</v>
+        <v>480539</v>
       </c>
       <c r="R5" t="n">
-        <v>6596485</v>
+        <v>6596612</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1085,6 +1096,11 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-01-26</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Endast en bål på lodyta</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1112,10 +1128,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122335180</v>
+        <v>122335213</v>
       </c>
       <c r="B6" t="n">
-        <v>56584</v>
+        <v>78734</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1128,43 +1144,26 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100138</v>
+        <v>6450</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Skuggblåslav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Hypogymnia vittata</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>stationär</t>
-        </is>
-      </c>
+          <t>(Ach.) Parrique</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1172,10 +1171,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>480403</v>
+        <v>480554</v>
       </c>
       <c r="R6" t="n">
-        <v>6596616</v>
+        <v>6596596</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1216,6 +1215,7 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 39826-2020 artfynd.xlsx
+++ b/artfynd/A 39826-2020 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122335149</v>
+        <v>122335180</v>
       </c>
       <c r="B2" t="n">
-        <v>78381</v>
+        <v>56584</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,30 +687,47 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6446</v>
+        <v>100138</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>stationär</t>
+        </is>
+      </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -718,10 +735,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>480442</v>
+        <v>480403</v>
       </c>
       <c r="R2" t="n">
-        <v>6596485</v>
+        <v>6596616</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -762,7 +779,6 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -781,10 +797,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122335180</v>
+        <v>122335159</v>
       </c>
       <c r="B3" t="n">
-        <v>56584</v>
+        <v>78291</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,47 +809,30 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100138</v>
+        <v>353</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>stationär</t>
-        </is>
-      </c>
+          <t>(Hoffm.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -841,10 +840,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>480403</v>
+        <v>480354</v>
       </c>
       <c r="R3" t="n">
-        <v>6596616</v>
+        <v>6596544</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -885,6 +884,7 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -903,10 +903,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122335159</v>
+        <v>122335205</v>
       </c>
       <c r="B4" t="n">
-        <v>78290</v>
+        <v>78809</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -915,29 +915,37 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>353</v>
+        <v>1249</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Norsk näverlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Platismatia norvegica</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
+          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="K4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
@@ -946,10 +954,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>480354</v>
+        <v>480539</v>
       </c>
       <c r="R4" t="n">
-        <v>6596544</v>
+        <v>6596612</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -982,6 +990,11 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-01-26</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Endast en bål på lodyta</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1009,10 +1022,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122335205</v>
+        <v>122335149</v>
       </c>
       <c r="B5" t="n">
-        <v>78808</v>
+        <v>78382</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1021,37 +1034,29 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1249</v>
+        <v>6446</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Norsk näverlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Platismatia norvegica</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
@@ -1060,10 +1065,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>480539</v>
+        <v>480442</v>
       </c>
       <c r="R5" t="n">
-        <v>6596612</v>
+        <v>6596485</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1096,11 +1101,6 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-01-26</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Endast en bål på lodyta</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1131,7 +1131,7 @@
         <v>122335213</v>
       </c>
       <c r="B6" t="n">
-        <v>78734</v>
+        <v>78735</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>

--- a/artfynd/A 39826-2020 artfynd.xlsx
+++ b/artfynd/A 39826-2020 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122335180</v>
+        <v>122335149</v>
       </c>
       <c r="B2" t="n">
-        <v>56584</v>
+        <v>78382</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,47 +687,30 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100138</v>
+        <v>6446</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>stationär</t>
-        </is>
-      </c>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -735,10 +718,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>480403</v>
+        <v>480442</v>
       </c>
       <c r="R2" t="n">
-        <v>6596616</v>
+        <v>6596485</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -779,6 +762,7 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -797,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122335159</v>
+        <v>122335213</v>
       </c>
       <c r="B3" t="n">
-        <v>78291</v>
+        <v>78735</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -809,25 +793,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>353</v>
+        <v>6450</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Skuggblåslav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hypogymnia vittata</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Parrique</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -840,10 +824,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>480354</v>
+        <v>480554</v>
       </c>
       <c r="R3" t="n">
-        <v>6596544</v>
+        <v>6596596</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -1022,10 +1006,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122335149</v>
+        <v>122335159</v>
       </c>
       <c r="B5" t="n">
-        <v>78382</v>
+        <v>78291</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1038,21 +1022,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6446</v>
+        <v>353</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1065,10 +1049,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>480442</v>
+        <v>480354</v>
       </c>
       <c r="R5" t="n">
-        <v>6596485</v>
+        <v>6596544</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1128,14 +1112,14 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122335213</v>
+        <v>122335180</v>
       </c>
       <c r="B6" t="n">
-        <v>78735</v>
+        <v>56584</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Godkänd baserat på observatörens uppgifter</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1144,26 +1128,43 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6450</v>
+        <v>100138</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Skuggblåslav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hypogymnia vittata</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Parrique</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>stationär</t>
+        </is>
+      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1171,10 +1172,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>480554</v>
+        <v>480403</v>
       </c>
       <c r="R6" t="n">
-        <v>6596596</v>
+        <v>6596616</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1215,7 +1216,6 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 39826-2020 artfynd.xlsx
+++ b/artfynd/A 39826-2020 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122335149</v>
+        <v>122335159</v>
       </c>
       <c r="B2" t="n">
-        <v>78382</v>
+        <v>78296</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6446</v>
+        <v>353</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -718,10 +718,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>480442</v>
+        <v>480354</v>
       </c>
       <c r="R2" t="n">
-        <v>6596485</v>
+        <v>6596544</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -784,7 +784,7 @@
         <v>122335213</v>
       </c>
       <c r="B3" t="n">
-        <v>78735</v>
+        <v>78740</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -890,7 +890,7 @@
         <v>122335205</v>
       </c>
       <c r="B4" t="n">
-        <v>78809</v>
+        <v>78814</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -1006,10 +1006,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122335159</v>
+        <v>122335149</v>
       </c>
       <c r="B5" t="n">
-        <v>78291</v>
+        <v>78387</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1022,21 +1022,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>353</v>
+        <v>6446</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1049,10 +1049,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>480354</v>
+        <v>480442</v>
       </c>
       <c r="R5" t="n">
-        <v>6596544</v>
+        <v>6596485</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1115,7 +1115,7 @@
         <v>122335180</v>
       </c>
       <c r="B6" t="n">
-        <v>56584</v>
+        <v>56589</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>

--- a/artfynd/A 39826-2020 artfynd.xlsx
+++ b/artfynd/A 39826-2020 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122335159</v>
+        <v>122335213</v>
       </c>
       <c r="B2" t="n">
-        <v>78296</v>
+        <v>78740</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>353</v>
+        <v>6450</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Skuggblåslav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hypogymnia vittata</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Parrique</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -718,10 +718,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>480354</v>
+        <v>480554</v>
       </c>
       <c r="R2" t="n">
-        <v>6596544</v>
+        <v>6596596</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122335213</v>
+        <v>122335205</v>
       </c>
       <c r="B3" t="n">
-        <v>78740</v>
+        <v>78814</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,29 +793,37 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6450</v>
+        <v>1249</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Skuggblåslav</t>
+          <t>Norsk näverlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hypogymnia vittata</t>
+          <t>Platismatia norvegica</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Parrique</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
+          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="K3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
@@ -824,10 +832,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>480554</v>
+        <v>480539</v>
       </c>
       <c r="R3" t="n">
-        <v>6596596</v>
+        <v>6596612</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -860,6 +868,11 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-01-26</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Endast en bål på lodyta</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -887,10 +900,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122335205</v>
+        <v>122335159</v>
       </c>
       <c r="B4" t="n">
-        <v>78814</v>
+        <v>78296</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -899,37 +912,29 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1249</v>
+        <v>353</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Norsk näverlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Platismatia norvegica</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>(Hoffm.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
@@ -938,10 +943,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>480539</v>
+        <v>480354</v>
       </c>
       <c r="R4" t="n">
-        <v>6596612</v>
+        <v>6596544</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -974,11 +979,6 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-01-26</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Endast en bål på lodyta</t>
         </is>
       </c>
       <c r="AD4" t="b">

--- a/artfynd/A 39826-2020 artfynd.xlsx
+++ b/artfynd/A 39826-2020 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>122335213</v>
       </c>
       <c r="B2" t="n">
-        <v>78740</v>
+        <v>78741</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -692,11 +692,6 @@
       </c>
       <c r="E2" t="n">
         <v>6450</v>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>Skuggblåslav</t>
-        </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -781,10 +776,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122335205</v>
+        <v>122335159</v>
       </c>
       <c r="B3" t="n">
-        <v>78814</v>
+        <v>78297</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,37 +788,24 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1249</v>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>Norsk näverlav</t>
-        </is>
+        <v>353</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Platismatia norvegica</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>(Hoffm.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
@@ -832,10 +814,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>480539</v>
+        <v>480354</v>
       </c>
       <c r="R3" t="n">
-        <v>6596612</v>
+        <v>6596544</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -868,11 +850,6 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-01-26</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Endast en bål på lodyta</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -900,10 +877,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122335159</v>
+        <v>122335205</v>
       </c>
       <c r="B4" t="n">
-        <v>78296</v>
+        <v>78815</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -912,29 +889,32 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>353</v>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>Dvärgbägarlav</t>
-        </is>
+        <v>1249</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Platismatia norvegica</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
+          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="K4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
@@ -943,10 +923,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>480354</v>
+        <v>480539</v>
       </c>
       <c r="R4" t="n">
-        <v>6596544</v>
+        <v>6596612</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -979,6 +959,11 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-01-26</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Endast en bål på lodyta</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1009,7 +994,7 @@
         <v>122335149</v>
       </c>
       <c r="B5" t="n">
-        <v>78387</v>
+        <v>78388</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1023,11 +1008,6 @@
       </c>
       <c r="E5" t="n">
         <v>6446</v>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>Kolflarnlav</t>
-        </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -1129,11 +1109,6 @@
       </c>
       <c r="E6" t="n">
         <v>100138</v>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>Tjäder</t>
-        </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>

--- a/artfynd/A 39826-2020 artfynd.xlsx
+++ b/artfynd/A 39826-2020 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122335213</v>
+        <v>122335149</v>
       </c>
       <c r="B2" t="n">
-        <v>78741</v>
+        <v>78392</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,20 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6450</v>
+        <v>6446</v>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Kolflarnlav</t>
+        </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hypogymnia vittata</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Parrique</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -713,10 +718,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>480554</v>
+        <v>480442</v>
       </c>
       <c r="R2" t="n">
-        <v>6596596</v>
+        <v>6596485</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -776,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122335159</v>
+        <v>122335213</v>
       </c>
       <c r="B3" t="n">
-        <v>78297</v>
+        <v>78745</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -788,20 +793,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>353</v>
+        <v>6450</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Skuggblåslav</t>
+        </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hypogymnia vittata</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Parrique</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -814,10 +824,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>480354</v>
+        <v>480554</v>
       </c>
       <c r="R3" t="n">
-        <v>6596544</v>
+        <v>6596596</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -877,10 +887,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122335205</v>
+        <v>122335159</v>
       </c>
       <c r="B4" t="n">
-        <v>78815</v>
+        <v>78301</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -889,32 +899,29 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1249</v>
+        <v>353</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Dvärgbägarlav</t>
+        </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Platismatia norvegica</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>(Hoffm.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
@@ -923,10 +930,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>480539</v>
+        <v>480354</v>
       </c>
       <c r="R4" t="n">
-        <v>6596612</v>
+        <v>6596544</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -959,11 +966,6 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-01-26</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Endast en bål på lodyta</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -991,10 +993,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122335149</v>
+        <v>122335205</v>
       </c>
       <c r="B5" t="n">
-        <v>78388</v>
+        <v>78819</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1003,24 +1005,37 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6446</v>
+        <v>1249</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Norsk näverlav</t>
+        </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Platismatia norvegica</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
+          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="K5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
@@ -1029,10 +1044,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>480442</v>
+        <v>480539</v>
       </c>
       <c r="R5" t="n">
-        <v>6596485</v>
+        <v>6596612</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1065,6 +1080,11 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-01-26</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Endast en bål på lodyta</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1095,7 +1115,7 @@
         <v>122335180</v>
       </c>
       <c r="B6" t="n">
-        <v>56589</v>
+        <v>56593</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1109,6 +1129,11 @@
       </c>
       <c r="E6" t="n">
         <v>100138</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>

--- a/artfynd/A 39826-2020 artfynd.xlsx
+++ b/artfynd/A 39826-2020 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122335149</v>
+        <v>122335213</v>
       </c>
       <c r="B2" t="n">
-        <v>78392</v>
+        <v>78745</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6446</v>
+        <v>6450</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Skuggblåslav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hypogymnia vittata</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Parrique</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -718,10 +718,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>480442</v>
+        <v>480554</v>
       </c>
       <c r="R2" t="n">
-        <v>6596485</v>
+        <v>6596596</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122335213</v>
+        <v>122335205</v>
       </c>
       <c r="B3" t="n">
-        <v>78745</v>
+        <v>78819</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,29 +793,37 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6450</v>
+        <v>1249</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Skuggblåslav</t>
+          <t>Norsk näverlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hypogymnia vittata</t>
+          <t>Platismatia norvegica</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Parrique</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
+          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="K3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
@@ -824,10 +832,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>480554</v>
+        <v>480539</v>
       </c>
       <c r="R3" t="n">
-        <v>6596596</v>
+        <v>6596612</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -860,6 +868,11 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-01-26</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Endast en bål på lodyta</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -887,10 +900,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122335159</v>
+        <v>122335149</v>
       </c>
       <c r="B4" t="n">
-        <v>78301</v>
+        <v>78392</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -903,21 +916,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>353</v>
+        <v>6446</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -930,10 +943,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>480354</v>
+        <v>480442</v>
       </c>
       <c r="R4" t="n">
-        <v>6596544</v>
+        <v>6596485</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -993,10 +1006,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122335205</v>
+        <v>122335159</v>
       </c>
       <c r="B5" t="n">
-        <v>78819</v>
+        <v>78301</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1005,37 +1018,29 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1249</v>
+        <v>353</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Norsk näverlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Platismatia norvegica</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>(Hoffm.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
@@ -1044,10 +1049,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>480539</v>
+        <v>480354</v>
       </c>
       <c r="R5" t="n">
-        <v>6596612</v>
+        <v>6596544</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1080,11 +1085,6 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-01-26</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Endast en bål på lodyta</t>
         </is>
       </c>
       <c r="AD5" t="b">

--- a/artfynd/A 39826-2020 artfynd.xlsx
+++ b/artfynd/A 39826-2020 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122335213</v>
+        <v>122335149</v>
       </c>
       <c r="B2" t="n">
-        <v>78745</v>
+        <v>78392</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6450</v>
+        <v>6446</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Skuggblåslav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hypogymnia vittata</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Parrique</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -718,10 +718,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>480554</v>
+        <v>480442</v>
       </c>
       <c r="R2" t="n">
-        <v>6596596</v>
+        <v>6596485</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122335205</v>
+        <v>122335213</v>
       </c>
       <c r="B3" t="n">
-        <v>78819</v>
+        <v>78745</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,37 +793,29 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1249</v>
+        <v>6450</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Norsk näverlav</t>
+          <t>Skuggblåslav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Platismatia norvegica</t>
+          <t>Hypogymnia vittata</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>(Ach.) Parrique</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
@@ -832,10 +824,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>480539</v>
+        <v>480554</v>
       </c>
       <c r="R3" t="n">
-        <v>6596612</v>
+        <v>6596596</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -868,11 +860,6 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-01-26</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Endast en bål på lodyta</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -900,10 +887,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122335149</v>
+        <v>122335205</v>
       </c>
       <c r="B4" t="n">
-        <v>78392</v>
+        <v>78819</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -912,29 +899,37 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6446</v>
+        <v>1249</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Norsk näverlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Platismatia norvegica</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
+          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="K4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
@@ -943,10 +938,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>480442</v>
+        <v>480539</v>
       </c>
       <c r="R4" t="n">
-        <v>6596485</v>
+        <v>6596612</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -979,6 +974,11 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-01-26</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Endast en bål på lodyta</t>
         </is>
       </c>
       <c r="AD4" t="b">

--- a/artfynd/A 39826-2020 artfynd.xlsx
+++ b/artfynd/A 39826-2020 artfynd.xlsx
@@ -887,10 +887,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122335205</v>
+        <v>122335159</v>
       </c>
       <c r="B4" t="n">
-        <v>78819</v>
+        <v>78301</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -899,37 +899,29 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1249</v>
+        <v>353</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Norsk näverlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Platismatia norvegica</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>(Hoffm.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
@@ -938,10 +930,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>480539</v>
+        <v>480354</v>
       </c>
       <c r="R4" t="n">
-        <v>6596612</v>
+        <v>6596544</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -974,11 +966,6 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-01-26</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Endast en bål på lodyta</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1006,10 +993,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122335159</v>
+        <v>122335205</v>
       </c>
       <c r="B5" t="n">
-        <v>78301</v>
+        <v>78819</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1018,29 +1005,37 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>353</v>
+        <v>1249</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Norsk näverlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Platismatia norvegica</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
+          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="K5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
@@ -1049,10 +1044,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>480354</v>
+        <v>480539</v>
       </c>
       <c r="R5" t="n">
-        <v>6596544</v>
+        <v>6596612</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1085,6 +1080,11 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-01-26</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Endast en bål på lodyta</t>
         </is>
       </c>
       <c r="AD5" t="b">

--- a/artfynd/A 39826-2020 artfynd.xlsx
+++ b/artfynd/A 39826-2020 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122335149</v>
+        <v>122335205</v>
       </c>
       <c r="B2" t="n">
-        <v>78392</v>
+        <v>78819</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,29 +687,37 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6446</v>
+        <v>1249</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Norsk näverlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Platismatia norvegica</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
+          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="K2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
@@ -718,10 +726,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>480442</v>
+        <v>480539</v>
       </c>
       <c r="R2" t="n">
-        <v>6596485</v>
+        <v>6596612</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -754,6 +762,11 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-01-26</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Endast en bål på lodyta</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -993,10 +1006,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122335205</v>
+        <v>122335149</v>
       </c>
       <c r="B5" t="n">
-        <v>78819</v>
+        <v>78392</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1005,37 +1018,29 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1249</v>
+        <v>6446</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Norsk näverlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Platismatia norvegica</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
@@ -1044,10 +1049,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>480539</v>
+        <v>480442</v>
       </c>
       <c r="R5" t="n">
-        <v>6596612</v>
+        <v>6596485</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1080,11 +1085,6 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-01-26</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Endast en bål på lodyta</t>
         </is>
       </c>
       <c r="AD5" t="b">

--- a/artfynd/A 39826-2020 artfynd.xlsx
+++ b/artfynd/A 39826-2020 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122335205</v>
+        <v>122335149</v>
       </c>
       <c r="B2" t="n">
-        <v>78819</v>
+        <v>78393</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,37 +687,29 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1249</v>
+        <v>6446</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Norsk näverlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Platismatia norvegica</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
@@ -726,10 +718,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>480539</v>
+        <v>480442</v>
       </c>
       <c r="R2" t="n">
-        <v>6596612</v>
+        <v>6596485</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -762,11 +754,6 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-01-26</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Endast en bål på lodyta</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -797,7 +784,7 @@
         <v>122335213</v>
       </c>
       <c r="B3" t="n">
-        <v>78745</v>
+        <v>78746</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -900,10 +887,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122335159</v>
+        <v>122335205</v>
       </c>
       <c r="B4" t="n">
-        <v>78301</v>
+        <v>78820</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -912,29 +899,37 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>353</v>
+        <v>1249</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Norsk näverlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Platismatia norvegica</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
+          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="K4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
@@ -943,10 +938,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>480354</v>
+        <v>480539</v>
       </c>
       <c r="R4" t="n">
-        <v>6596544</v>
+        <v>6596612</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -979,6 +974,11 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-01-26</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Endast en bål på lodyta</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1006,10 +1006,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122335149</v>
+        <v>122335159</v>
       </c>
       <c r="B5" t="n">
-        <v>78392</v>
+        <v>78302</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1022,21 +1022,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6446</v>
+        <v>353</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1049,10 +1049,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>480442</v>
+        <v>480354</v>
       </c>
       <c r="R5" t="n">
-        <v>6596485</v>
+        <v>6596544</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1115,7 +1115,7 @@
         <v>122335180</v>
       </c>
       <c r="B6" t="n">
-        <v>56593</v>
+        <v>56594</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>

--- a/artfynd/A 39826-2020 artfynd.xlsx
+++ b/artfynd/A 39826-2020 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AY16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1232,6 +1232,1247 @@
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>123989116</v>
+      </c>
+      <c r="B7" t="n">
+        <v>57507</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Lilla Bergtjärnen, Lilla Bergtjärnen, Vstm</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>480299</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6596637</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Hällefors</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Grythyttan</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2025-04-12</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>09:41</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2025-04-12</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>09:41</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>På jakt efter hästmyror i grövre gran.</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Jim Hellquist</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Jim Hellquist</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>123987670</v>
+      </c>
+      <c r="B8" t="n">
+        <v>57491</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Rangelbäcken, Rangelbäcken, Vstm</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>480411</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6596749</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Hällefors</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Grythyttan</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2025-04-12</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>08:51</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2025-04-12</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>08:51</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Ringbarkning i tallöverståndare.</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Jim Hellquist</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Jim Hellquist</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>123987555</v>
+      </c>
+      <c r="B9" t="n">
+        <v>57491</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Rangelbäcken, Rangelbäcken, Vstm</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>480411</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6596690</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Hällefors</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Grythyttan</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2025-04-12</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>08:44</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2025-04-12</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>08:44</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Ringbarkning i äldre tall.</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Jim Hellquist</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Jim Hellquist</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>123991709</v>
+      </c>
+      <c r="B10" t="n">
+        <v>79406</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Stora Bergtjärnen, Stora Bergtjärnen, Vstm</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>480553</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6596500</v>
+      </c>
+      <c r="S10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Hällefors</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Grythyttan</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2025-04-12</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>10:41</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2025-04-12</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>10:41</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Jim Hellquist</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Jim Hellquist</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>123988405</v>
+      </c>
+      <c r="B11" t="n">
+        <v>78788</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Rangelbäcken, Rangelbäcken, Vstm</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>480313</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6596806</v>
+      </c>
+      <c r="S11" t="n">
+        <v>10</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Hällefors</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Grythyttan</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2025-04-12</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>09:18</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2025-04-12</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>09:18</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Jim Hellquist</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Jim Hellquist</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>123987592</v>
+      </c>
+      <c r="B12" t="n">
+        <v>57644</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>i par</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>par i lämplig häckbiotop</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Rangelbäcken, Rangelbäcken, Vstm</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>480404</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6596699</v>
+      </c>
+      <c r="S12" t="n">
+        <v>10</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Hällefors</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Grythyttan</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2025-04-12</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>08:46</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2025-04-12</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>08:46</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Jim Hellquist</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Jim Hellquist</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>123987634</v>
+      </c>
+      <c r="B13" t="n">
+        <v>78788</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Rangelbäcken, Rangelbäcken, Vstm</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>480394</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6596739</v>
+      </c>
+      <c r="S13" t="n">
+        <v>10</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Hällefors</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Grythyttan</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2025-04-12</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>08:50</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2025-04-12</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>08:50</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Högt upp i tallöverståndare.</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Jim Hellquist</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Jim Hellquist</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>123988025</v>
+      </c>
+      <c r="B14" t="n">
+        <v>57491</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>obs i häcktid, lämplig biotop</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Rangelbäcken, Rangelbäcken, Vstm</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>480363</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6596775</v>
+      </c>
+      <c r="S14" t="n">
+        <v>10</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Hällefors</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Grythyttan</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2025-04-12</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>09:05</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2025-04-12</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>09:05</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Födosökande på gran.</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Jim Hellquist</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Jim Hellquist</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>123989693</v>
+      </c>
+      <c r="B15" t="n">
+        <v>56700</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Stora Bergtjärnen, Stora Bergtjärnen, Vstm</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>480384</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6596389</v>
+      </c>
+      <c r="S15" t="n">
+        <v>10</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Hällefors</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Grythyttan</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2025-04-12</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>09:52</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2025-04-12</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>09:52</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Badgrop.</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Jim Hellquist</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Jim Hellquist</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>123987786</v>
+      </c>
+      <c r="B16" t="n">
+        <v>57507</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Rangelbäcken, Rangelbäcken, Vstm</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>480379</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6596690</v>
+      </c>
+      <c r="S16" t="n">
+        <v>10</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Hällefors</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Grythyttan</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2025-04-12</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>08:58</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2025-04-12</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>08:58</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Bohål i tallöverståndare passande för pärluggla.</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Jim Hellquist</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Jim Hellquist</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 39826-2020 artfynd.xlsx
+++ b/artfynd/A 39826-2020 artfynd.xlsx
@@ -1234,10 +1234,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123989116</v>
+        <v>123987670</v>
       </c>
       <c r="B7" t="n">
-        <v>57507</v>
+        <v>57491</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1250,16 +1250,16 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -1267,7 +1267,11 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr"/>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K7" t="inlineStr">
         <is>
           <t>adult</t>
@@ -1275,19 +1279,19 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Lilla Bergtjärnen, Lilla Bergtjärnen, Vstm</t>
+          <t>Rangelbäcken, Rangelbäcken, Vstm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>480299</v>
+        <v>480411</v>
       </c>
       <c r="R7" t="n">
-        <v>6596637</v>
+        <v>6596749</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1319,7 +1323,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>09:41</t>
+          <t>08:51</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1329,12 +1333,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>09:41</t>
+          <t>08:51</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>På jakt efter hästmyror i grövre gran.</t>
+          <t>Ringbarkning i tallöverståndare.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1361,10 +1365,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123987670</v>
+        <v>123989116</v>
       </c>
       <c r="B8" t="n">
-        <v>57491</v>
+        <v>57507</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1377,16 +1381,16 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1394,11 +1398,7 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="K8" t="inlineStr">
         <is>
           <t>adult</t>
@@ -1406,19 +1406,19 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Rangelbäcken, Rangelbäcken, Vstm</t>
+          <t>Lilla Bergtjärnen, Lilla Bergtjärnen, Vstm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>480411</v>
+        <v>480299</v>
       </c>
       <c r="R8" t="n">
-        <v>6596749</v>
+        <v>6596637</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1450,7 +1450,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>08:51</t>
+          <t>09:41</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1460,12 +1460,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>08:51</t>
+          <t>09:41</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Ringbarkning i tallöverståndare.</t>
+          <t>På jakt efter hästmyror i grövre gran.</t>
         </is>
       </c>
       <c r="AD8" t="b">

--- a/artfynd/A 39826-2020 artfynd.xlsx
+++ b/artfynd/A 39826-2020 artfynd.xlsx
@@ -1234,10 +1234,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123987670</v>
+        <v>123989693</v>
       </c>
       <c r="B7" t="n">
-        <v>57491</v>
+        <v>56700</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1246,32 +1246,28 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>100138</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="K7" t="inlineStr">
         <is>
           <t>adult</t>
@@ -1284,14 +1280,14 @@
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Rangelbäcken, Rangelbäcken, Vstm</t>
+          <t>Stora Bergtjärnen, Stora Bergtjärnen, Vstm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>480411</v>
+        <v>480384</v>
       </c>
       <c r="R7" t="n">
-        <v>6596749</v>
+        <v>6596389</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1323,7 +1319,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>08:51</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1333,12 +1329,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>08:51</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Ringbarkning i tallöverståndare.</t>
+          <t>Badgrop.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1365,10 +1361,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123989116</v>
+        <v>123987634</v>
       </c>
       <c r="B8" t="n">
-        <v>57507</v>
+        <v>78788</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1381,44 +1377,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Lilla Bergtjärnen, Lilla Bergtjärnen, Vstm</t>
+          <t>Rangelbäcken, Rangelbäcken, Vstm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>480299</v>
+        <v>480394</v>
       </c>
       <c r="R8" t="n">
-        <v>6596637</v>
+        <v>6596739</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1450,7 +1436,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>09:41</t>
+          <t>08:50</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1460,12 +1446,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>09:41</t>
+          <t>08:50</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>På jakt efter hästmyror i grövre gran.</t>
+          <t>Högt upp i tallöverståndare.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1492,10 +1478,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123987555</v>
+        <v>123988405</v>
       </c>
       <c r="B9" t="n">
-        <v>57491</v>
+        <v>78788</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1508,48 +1494,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Rangelbäcken, Rangelbäcken, Vstm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>480411</v>
+        <v>480313</v>
       </c>
       <c r="R9" t="n">
-        <v>6596690</v>
+        <v>6596806</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1581,7 +1553,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>08:44</t>
+          <t>09:18</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1591,12 +1563,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>08:44</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Ringbarkning i äldre tall.</t>
+          <t>09:18</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1623,10 +1590,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123991709</v>
+        <v>123988025</v>
       </c>
       <c r="B10" t="n">
-        <v>79406</v>
+        <v>57491</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1639,34 +1606,48 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6453</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>obs i häcktid, lämplig biotop</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Stora Bergtjärnen, Stora Bergtjärnen, Vstm</t>
+          <t>Rangelbäcken, Rangelbäcken, Vstm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>480553</v>
+        <v>480363</v>
       </c>
       <c r="R10" t="n">
-        <v>6596500</v>
+        <v>6596775</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1698,7 +1679,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>10:41</t>
+          <t>09:05</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1708,7 +1689,12 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>10:41</t>
+          <t>09:05</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Födosökande på gran.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1735,10 +1721,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123988405</v>
+        <v>123987555</v>
       </c>
       <c r="B11" t="n">
-        <v>78788</v>
+        <v>57491</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1751,34 +1737,48 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Rangelbäcken, Rangelbäcken, Vstm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>480313</v>
+        <v>480411</v>
       </c>
       <c r="R11" t="n">
-        <v>6596806</v>
+        <v>6596690</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1810,7 +1810,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>09:18</t>
+          <t>08:44</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1820,7 +1820,12 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>09:18</t>
+          <t>08:44</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Ringbarkning i äldre tall.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1847,10 +1852,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123987592</v>
+        <v>123987670</v>
       </c>
       <c r="B12" t="n">
-        <v>57644</v>
+        <v>57491</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1863,26 +1868,26 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -1890,14 +1895,9 @@
           <t>adult</t>
         </is>
       </c>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t>i par</t>
-        </is>
-      </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>par i lämplig häckbiotop</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
@@ -1906,10 +1906,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>480404</v>
+        <v>480411</v>
       </c>
       <c r="R12" t="n">
-        <v>6596699</v>
+        <v>6596749</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1941,7 +1941,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>08:46</t>
+          <t>08:51</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1951,7 +1951,12 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>08:46</t>
+          <t>08:51</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Ringbarkning i tallöverståndare.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1978,10 +1983,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>123987634</v>
+        <v>123987592</v>
       </c>
       <c r="B13" t="n">
-        <v>78788</v>
+        <v>57644</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1994,34 +1999,53 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>i par</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>par i lämplig häckbiotop</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Rangelbäcken, Rangelbäcken, Vstm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>480394</v>
+        <v>480404</v>
       </c>
       <c r="R13" t="n">
-        <v>6596739</v>
+        <v>6596699</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2053,7 +2077,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>08:50</t>
+          <t>08:46</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2063,12 +2087,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>08:50</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Högt upp i tallöverståndare.</t>
+          <t>08:46</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2095,10 +2114,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>123988025</v>
+        <v>123987786</v>
       </c>
       <c r="B14" t="n">
-        <v>57491</v>
+        <v>57507</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2111,16 +2130,16 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -2128,19 +2147,10 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
+      <c r="I14" t="inlineStr"/>
       <c r="M14" t="inlineStr">
         <is>
-          <t>obs i häcktid, lämplig biotop</t>
+          <t>gammalt bo</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
@@ -2149,10 +2159,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>480363</v>
+        <v>480379</v>
       </c>
       <c r="R14" t="n">
-        <v>6596775</v>
+        <v>6596690</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2184,7 +2194,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>09:05</t>
+          <t>08:58</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2194,12 +2204,12 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>09:05</t>
+          <t>08:58</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Födosökande på gran.</t>
+          <t>Bohål i tallöverståndare passande för pärluggla.</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2226,10 +2236,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>123989693</v>
+        <v>123991709</v>
       </c>
       <c r="B15" t="n">
-        <v>56700</v>
+        <v>79406</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2238,48 +2248,38 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100138</v>
+        <v>6453</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Stora Bergtjärnen, Stora Bergtjärnen, Vstm</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>480384</v>
+        <v>480553</v>
       </c>
       <c r="R15" t="n">
-        <v>6596389</v>
+        <v>6596500</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2311,7 +2311,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>10:41</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2321,12 +2321,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>09:52</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Badgrop.</t>
+          <t>10:41</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2353,7 +2348,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>123987786</v>
+        <v>123989116</v>
       </c>
       <c r="B16" t="n">
         <v>57507</v>
@@ -2387,21 +2382,26 @@
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>gammalt bo</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Rangelbäcken, Rangelbäcken, Vstm</t>
+          <t>Lilla Bergtjärnen, Lilla Bergtjärnen, Vstm</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>480379</v>
+        <v>480299</v>
       </c>
       <c r="R16" t="n">
-        <v>6596690</v>
+        <v>6596637</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2433,7 +2433,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>08:58</t>
+          <t>09:41</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2443,12 +2443,12 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>08:58</t>
+          <t>09:41</t>
         </is>
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Bohål i tallöverståndare passande för pärluggla.</t>
+          <t>På jakt efter hästmyror i grövre gran.</t>
         </is>
       </c>
       <c r="AD16" t="b">

--- a/artfynd/A 39826-2020 artfynd.xlsx
+++ b/artfynd/A 39826-2020 artfynd.xlsx
@@ -2236,10 +2236,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>123991709</v>
+        <v>123989116</v>
       </c>
       <c r="B15" t="n">
-        <v>79406</v>
+        <v>57507</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2252,34 +2252,44 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Stora Bergtjärnen, Stora Bergtjärnen, Vstm</t>
+          <t>Lilla Bergtjärnen, Lilla Bergtjärnen, Vstm</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>480553</v>
+        <v>480299</v>
       </c>
       <c r="R15" t="n">
-        <v>6596500</v>
+        <v>6596637</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2311,7 +2321,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>10:41</t>
+          <t>09:41</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2321,7 +2331,12 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>10:41</t>
+          <t>09:41</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>På jakt efter hästmyror i grövre gran.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2348,10 +2363,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>123989116</v>
+        <v>123991709</v>
       </c>
       <c r="B16" t="n">
-        <v>57507</v>
+        <v>79406</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2364,44 +2379,34 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="K16" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Lilla Bergtjärnen, Lilla Bergtjärnen, Vstm</t>
+          <t>Stora Bergtjärnen, Stora Bergtjärnen, Vstm</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>480299</v>
+        <v>480553</v>
       </c>
       <c r="R16" t="n">
-        <v>6596637</v>
+        <v>6596500</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2433,7 +2438,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>09:41</t>
+          <t>10:41</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2443,12 +2448,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>09:41</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>På jakt efter hästmyror i grövre gran.</t>
+          <t>10:41</t>
         </is>
       </c>
       <c r="AD16" t="b">

--- a/artfynd/A 39826-2020 artfynd.xlsx
+++ b/artfynd/A 39826-2020 artfynd.xlsx
@@ -1234,10 +1234,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123989693</v>
+        <v>123987634</v>
       </c>
       <c r="B7" t="n">
-        <v>56700</v>
+        <v>78788</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1246,48 +1246,38 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Stora Bergtjärnen, Stora Bergtjärnen, Vstm</t>
+          <t>Rangelbäcken, Rangelbäcken, Vstm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>480384</v>
+        <v>480394</v>
       </c>
       <c r="R7" t="n">
-        <v>6596389</v>
+        <v>6596739</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1319,7 +1309,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>08:50</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1329,12 +1319,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>08:50</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Badgrop.</t>
+          <t>Högt upp i tallöverståndare.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1361,10 +1351,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123987634</v>
+        <v>123988025</v>
       </c>
       <c r="B8" t="n">
-        <v>78788</v>
+        <v>57491</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1377,34 +1367,48 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>obs i häcktid, lämplig biotop</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Rangelbäcken, Rangelbäcken, Vstm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>480394</v>
+        <v>480363</v>
       </c>
       <c r="R8" t="n">
-        <v>6596739</v>
+        <v>6596775</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1436,7 +1440,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>08:50</t>
+          <t>09:05</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1446,12 +1450,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>08:50</t>
+          <t>09:05</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Högt upp i tallöverståndare.</t>
+          <t>Födosökande på gran.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1478,10 +1482,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123988405</v>
+        <v>123989116</v>
       </c>
       <c r="B9" t="n">
-        <v>78788</v>
+        <v>57507</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1494,34 +1498,44 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Rangelbäcken, Rangelbäcken, Vstm</t>
+          <t>Lilla Bergtjärnen, Lilla Bergtjärnen, Vstm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>480313</v>
+        <v>480299</v>
       </c>
       <c r="R9" t="n">
-        <v>6596806</v>
+        <v>6596637</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1553,7 +1567,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>09:18</t>
+          <t>09:41</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1563,7 +1577,12 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>09:18</t>
+          <t>09:41</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>På jakt efter hästmyror i grövre gran.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1590,10 +1609,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123988025</v>
+        <v>123989672</v>
       </c>
       <c r="B10" t="n">
-        <v>57491</v>
+        <v>56700</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1602,52 +1621,53 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>100138</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="K10" t="inlineStr">
         <is>
           <t>adult</t>
         </is>
       </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>obs i häcktid, lämplig biotop</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Rangelbäcken, Rangelbäcken, Vstm</t>
+          <t>Stora Bergtjärnen, Stora Bergtjärnen, Vstm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>480363</v>
+        <v>480384</v>
       </c>
       <c r="R10" t="n">
-        <v>6596775</v>
+        <v>6596389</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1679,7 +1699,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>09:05</t>
+          <t>09:51</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1689,12 +1709,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>09:05</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Födosökande på gran.</t>
+          <t>09:51</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1721,10 +1736,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123987555</v>
+        <v>123987592</v>
       </c>
       <c r="B11" t="n">
-        <v>57491</v>
+        <v>57644</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1737,26 +1752,26 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -1764,9 +1779,14 @@
           <t>adult</t>
         </is>
       </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>i par</t>
+        </is>
+      </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>par i lämplig häckbiotop</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
@@ -1775,10 +1795,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>480411</v>
+        <v>480404</v>
       </c>
       <c r="R11" t="n">
-        <v>6596690</v>
+        <v>6596699</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1810,7 +1830,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>08:44</t>
+          <t>08:46</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1820,12 +1840,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>08:44</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Ringbarkning i äldre tall.</t>
+          <t>08:46</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1852,10 +1867,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123987670</v>
+        <v>123987786</v>
       </c>
       <c r="B12" t="n">
-        <v>57491</v>
+        <v>57507</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1868,16 +1883,16 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1885,19 +1900,10 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="M12" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>gammalt bo</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
@@ -1906,10 +1912,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>480411</v>
+        <v>480379</v>
       </c>
       <c r="R12" t="n">
-        <v>6596749</v>
+        <v>6596690</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1941,7 +1947,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>08:51</t>
+          <t>08:58</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1951,12 +1957,12 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>08:51</t>
+          <t>08:58</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Ringbarkning i tallöverståndare.</t>
+          <t>Bohål i tallöverståndare passande för pärluggla.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1983,10 +1989,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>123987592</v>
+        <v>123988405</v>
       </c>
       <c r="B13" t="n">
-        <v>57644</v>
+        <v>78788</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1999,53 +2005,34 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L13" t="inlineStr">
-        <is>
-          <t>i par</t>
-        </is>
-      </c>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>par i lämplig häckbiotop</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Rangelbäcken, Rangelbäcken, Vstm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>480404</v>
+        <v>480313</v>
       </c>
       <c r="R13" t="n">
-        <v>6596699</v>
+        <v>6596806</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2077,7 +2064,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>08:46</t>
+          <t>09:18</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2087,7 +2074,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>08:46</t>
+          <t>09:18</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2114,10 +2101,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>123987786</v>
+        <v>123987555</v>
       </c>
       <c r="B14" t="n">
-        <v>57507</v>
+        <v>57491</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2130,16 +2117,16 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -2147,10 +2134,19 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I14" t="inlineStr"/>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>gammalt bo</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
@@ -2159,7 +2155,7 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>480379</v>
+        <v>480411</v>
       </c>
       <c r="R14" t="n">
         <v>6596690</v>
@@ -2194,7 +2190,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>08:58</t>
+          <t>08:44</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2204,12 +2200,12 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>08:58</t>
+          <t>08:44</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Bohål i tallöverståndare passande för pärluggla.</t>
+          <t>Ringbarkning i äldre tall.</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2236,10 +2232,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>123989116</v>
+        <v>123991709</v>
       </c>
       <c r="B15" t="n">
-        <v>57507</v>
+        <v>79406</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2252,44 +2248,34 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Lilla Bergtjärnen, Lilla Bergtjärnen, Vstm</t>
+          <t>Stora Bergtjärnen, Stora Bergtjärnen, Vstm</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>480299</v>
+        <v>480553</v>
       </c>
       <c r="R15" t="n">
-        <v>6596637</v>
+        <v>6596500</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2321,7 +2307,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>09:41</t>
+          <t>10:41</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2331,12 +2317,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>09:41</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>På jakt efter hästmyror i grövre gran.</t>
+          <t>10:41</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2363,10 +2344,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>123991709</v>
+        <v>123987670</v>
       </c>
       <c r="B16" t="n">
-        <v>79406</v>
+        <v>57491</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2379,34 +2360,48 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6453</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Stora Bergtjärnen, Stora Bergtjärnen, Vstm</t>
+          <t>Rangelbäcken, Rangelbäcken, Vstm</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>480553</v>
+        <v>480411</v>
       </c>
       <c r="R16" t="n">
-        <v>6596500</v>
+        <v>6596749</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2438,7 +2433,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>10:41</t>
+          <t>08:51</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2448,7 +2443,12 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>10:41</t>
+          <t>08:51</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Ringbarkning i tallöverståndare.</t>
         </is>
       </c>
       <c r="AD16" t="b">

--- a/artfynd/A 39826-2020 artfynd.xlsx
+++ b/artfynd/A 39826-2020 artfynd.xlsx
@@ -1234,10 +1234,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123987634</v>
+        <v>123987670</v>
       </c>
       <c r="B7" t="n">
-        <v>78788</v>
+        <v>57491</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1250,34 +1250,48 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Rangelbäcken, Rangelbäcken, Vstm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>480394</v>
+        <v>480411</v>
       </c>
       <c r="R7" t="n">
-        <v>6596739</v>
+        <v>6596749</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1309,7 +1323,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>08:50</t>
+          <t>08:51</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1319,12 +1333,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>08:50</t>
+          <t>08:51</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Högt upp i tallöverståndare.</t>
+          <t>Ringbarkning i tallöverståndare.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1351,10 +1365,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123988025</v>
+        <v>123988405</v>
       </c>
       <c r="B8" t="n">
-        <v>57491</v>
+        <v>78788</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1367,48 +1381,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>obs i häcktid, lämplig biotop</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Rangelbäcken, Rangelbäcken, Vstm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>480363</v>
+        <v>480313</v>
       </c>
       <c r="R8" t="n">
-        <v>6596775</v>
+        <v>6596806</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1440,7 +1440,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>09:05</t>
+          <t>09:18</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1450,12 +1450,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>09:05</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Födosökande på gran.</t>
+          <t>09:18</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1482,10 +1477,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123989116</v>
+        <v>123989693</v>
       </c>
       <c r="B9" t="n">
-        <v>57507</v>
+        <v>56700</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1494,25 +1489,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100049</v>
+        <v>100138</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1523,19 +1518,19 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Lilla Bergtjärnen, Lilla Bergtjärnen, Vstm</t>
+          <t>Stora Bergtjärnen, Stora Bergtjärnen, Vstm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>480299</v>
+        <v>480384</v>
       </c>
       <c r="R9" t="n">
-        <v>6596637</v>
+        <v>6596389</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1567,7 +1562,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>09:41</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1577,12 +1572,12 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>09:41</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>På jakt efter hästmyror i grövre gran.</t>
+          <t>Badgrop.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1609,10 +1604,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123989672</v>
+        <v>123989116</v>
       </c>
       <c r="B10" t="n">
-        <v>56700</v>
+        <v>57507</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1621,25 +1616,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100138</v>
+        <v>100049</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1648,26 +1643,21 @@
           <t>adult</t>
         </is>
       </c>
-      <c r="L10" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Stora Bergtjärnen, Stora Bergtjärnen, Vstm</t>
+          <t>Lilla Bergtjärnen, Lilla Bergtjärnen, Vstm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>480384</v>
+        <v>480299</v>
       </c>
       <c r="R10" t="n">
-        <v>6596389</v>
+        <v>6596637</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1699,7 +1689,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>09:51</t>
+          <t>09:41</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1709,7 +1699,12 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>09:51</t>
+          <t>09:41</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>På jakt efter hästmyror i grövre gran.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1736,10 +1731,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123987592</v>
+        <v>123991709</v>
       </c>
       <c r="B11" t="n">
-        <v>57644</v>
+        <v>79406</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1752,53 +1747,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>103021</v>
+        <v>6453</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L11" t="inlineStr">
-        <is>
-          <t>i par</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>par i lämplig häckbiotop</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Rangelbäcken, Rangelbäcken, Vstm</t>
+          <t>Stora Bergtjärnen, Stora Bergtjärnen, Vstm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>480404</v>
+        <v>480553</v>
       </c>
       <c r="R11" t="n">
-        <v>6596699</v>
+        <v>6596500</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1830,7 +1806,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>08:46</t>
+          <t>10:41</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1840,7 +1816,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>08:46</t>
+          <t>10:41</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1989,10 +1965,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>123988405</v>
+        <v>123988025</v>
       </c>
       <c r="B13" t="n">
-        <v>78788</v>
+        <v>57491</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2005,34 +1981,48 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>obs i häcktid, lämplig biotop</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Rangelbäcken, Rangelbäcken, Vstm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>480313</v>
+        <v>480363</v>
       </c>
       <c r="R13" t="n">
-        <v>6596806</v>
+        <v>6596775</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2064,7 +2054,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>09:18</t>
+          <t>09:05</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2074,7 +2064,12 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>09:18</t>
+          <t>09:05</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Födosökande på gran.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2232,10 +2227,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>123991709</v>
+        <v>123987592</v>
       </c>
       <c r="B15" t="n">
-        <v>79406</v>
+        <v>57644</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2248,34 +2243,53 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6453</v>
+        <v>103021</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>i par</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>par i lämplig häckbiotop</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Stora Bergtjärnen, Stora Bergtjärnen, Vstm</t>
+          <t>Rangelbäcken, Rangelbäcken, Vstm</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>480553</v>
+        <v>480404</v>
       </c>
       <c r="R15" t="n">
-        <v>6596500</v>
+        <v>6596699</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2307,7 +2321,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>10:41</t>
+          <t>08:46</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2317,7 +2331,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>10:41</t>
+          <t>08:46</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2344,10 +2358,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>123987670</v>
+        <v>123987634</v>
       </c>
       <c r="B16" t="n">
-        <v>57491</v>
+        <v>78788</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2360,48 +2374,34 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K16" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Rangelbäcken, Rangelbäcken, Vstm</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>480411</v>
+        <v>480394</v>
       </c>
       <c r="R16" t="n">
-        <v>6596749</v>
+        <v>6596739</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2433,7 +2433,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>08:51</t>
+          <t>08:50</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2443,12 +2443,12 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>08:51</t>
+          <t>08:50</t>
         </is>
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Ringbarkning i tallöverståndare.</t>
+          <t>Högt upp i tallöverståndare.</t>
         </is>
       </c>
       <c r="AD16" t="b">

--- a/artfynd/A 39826-2020 artfynd.xlsx
+++ b/artfynd/A 39826-2020 artfynd.xlsx
@@ -1234,7 +1234,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123987634</v>
+        <v>123988405</v>
       </c>
       <c r="B7" t="n">
         <v>78810</v>
@@ -1274,10 +1274,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>480394</v>
+        <v>480313</v>
       </c>
       <c r="R7" t="n">
-        <v>6596739</v>
+        <v>6596806</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1309,7 +1309,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>08:50</t>
+          <t>09:18</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1319,12 +1319,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>08:50</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Högt upp i tallöverståndare.</t>
+          <t>09:18</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1463,7 +1458,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123988405</v>
+        <v>123987634</v>
       </c>
       <c r="B9" t="n">
         <v>78810</v>
@@ -1503,10 +1498,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>480313</v>
+        <v>480394</v>
       </c>
       <c r="R9" t="n">
-        <v>6596806</v>
+        <v>6596739</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1538,7 +1533,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>09:18</t>
+          <t>08:50</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1548,7 +1543,12 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>09:18</t>
+          <t>08:50</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Högt upp i tallöverståndare.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1575,14 +1575,14 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123987670</v>
+        <v>123987786</v>
       </c>
       <c r="B10" t="n">
-        <v>57513</v>
+        <v>57529</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Behöver inte valideras</t>
+          <t>Godkänd baserat på observatörens uppgifter</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1591,16 +1591,16 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1608,19 +1608,10 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="M10" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>gammalt bo</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
@@ -1629,10 +1620,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>480411</v>
+        <v>480379</v>
       </c>
       <c r="R10" t="n">
-        <v>6596749</v>
+        <v>6596690</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1664,7 +1655,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>08:51</t>
+          <t>08:58</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1674,12 +1665,12 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>08:51</t>
+          <t>08:58</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Ringbarkning i tallöverståndare.</t>
+          <t>Bohål i tallöverståndare passande för pärluggla.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1706,10 +1697,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123989116</v>
+        <v>123988025</v>
       </c>
       <c r="B11" t="n">
-        <v>57529</v>
+        <v>57513</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1722,16 +1713,16 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1739,7 +1730,11 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr"/>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K11" t="inlineStr">
         <is>
           <t>adult</t>
@@ -1747,19 +1742,19 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>obs i häcktid, lämplig biotop</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Lilla Bergtjärnen, Lilla Bergtjärnen, Vstm</t>
+          <t>Rangelbäcken, Rangelbäcken, Vstm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>480299</v>
+        <v>480363</v>
       </c>
       <c r="R11" t="n">
-        <v>6596637</v>
+        <v>6596775</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1791,7 +1786,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>09:41</t>
+          <t>09:05</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1801,12 +1796,12 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>09:41</t>
+          <t>09:05</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>På jakt efter hästmyror i grövre gran.</t>
+          <t>Födosökande på gran.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1833,10 +1828,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123987786</v>
+        <v>123987592</v>
       </c>
       <c r="B12" t="n">
-        <v>57529</v>
+        <v>57666</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1849,27 +1844,41 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100049</v>
+        <v>103021</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>i par</t>
+        </is>
+      </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>gammalt bo</t>
+          <t>par i lämplig häckbiotop</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
@@ -1878,10 +1887,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>480379</v>
+        <v>480404</v>
       </c>
       <c r="R12" t="n">
-        <v>6596690</v>
+        <v>6596699</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1913,7 +1922,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>08:58</t>
+          <t>08:46</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1923,12 +1932,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>08:58</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Bohål i tallöverståndare passande för pärluggla.</t>
+          <t>08:46</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2213,10 +2217,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>123987592</v>
+        <v>123989116</v>
       </c>
       <c r="B15" t="n">
-        <v>57666</v>
+        <v>57529</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2229,53 +2233,44 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>103021</v>
+        <v>100049</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
       <c r="K15" t="inlineStr">
         <is>
           <t>adult</t>
         </is>
       </c>
-      <c r="L15" t="inlineStr">
-        <is>
-          <t>i par</t>
-        </is>
-      </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>par i lämplig häckbiotop</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Rangelbäcken, Rangelbäcken, Vstm</t>
+          <t>Lilla Bergtjärnen, Lilla Bergtjärnen, Vstm</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>480404</v>
+        <v>480299</v>
       </c>
       <c r="R15" t="n">
-        <v>6596699</v>
+        <v>6596637</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2307,7 +2302,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>08:46</t>
+          <t>09:41</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2317,7 +2312,12 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>08:46</t>
+          <t>09:41</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>På jakt efter hästmyror i grövre gran.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2344,14 +2344,14 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>123988025</v>
+        <v>123987670</v>
       </c>
       <c r="B16" t="n">
         <v>57513</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
+          <t>Behöver inte valideras</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2389,7 +2389,7 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>obs i häcktid, lämplig biotop</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
@@ -2398,10 +2398,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>480363</v>
+        <v>480411</v>
       </c>
       <c r="R16" t="n">
-        <v>6596775</v>
+        <v>6596749</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2433,7 +2433,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>09:05</t>
+          <t>08:51</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2443,12 +2443,12 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>09:05</t>
+          <t>08:51</t>
         </is>
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Födosökande på gran.</t>
+          <t>Ringbarkning i tallöverståndare.</t>
         </is>
       </c>
       <c r="AD16" t="b">

--- a/artfynd/A 39826-2020 artfynd.xlsx
+++ b/artfynd/A 39826-2020 artfynd.xlsx
@@ -1346,10 +1346,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123991709</v>
+        <v>123987634</v>
       </c>
       <c r="B8" t="n">
-        <v>79428</v>
+        <v>78810</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1362,34 +1362,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Stora Bergtjärnen, Stora Bergtjärnen, Vstm</t>
+          <t>Rangelbäcken, Rangelbäcken, Vstm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>480553</v>
+        <v>480394</v>
       </c>
       <c r="R8" t="n">
-        <v>6596500</v>
+        <v>6596739</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1421,7 +1421,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>10:41</t>
+          <t>08:50</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1431,7 +1431,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>10:41</t>
+          <t>08:50</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Högt upp i tallöverståndare.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1458,10 +1463,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123987634</v>
+        <v>123991709</v>
       </c>
       <c r="B9" t="n">
-        <v>78810</v>
+        <v>79428</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1474,34 +1479,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Rangelbäcken, Rangelbäcken, Vstm</t>
+          <t>Stora Bergtjärnen, Stora Bergtjärnen, Vstm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>480394</v>
+        <v>480553</v>
       </c>
       <c r="R9" t="n">
-        <v>6596739</v>
+        <v>6596500</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1533,7 +1538,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>08:50</t>
+          <t>10:41</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1543,12 +1548,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>08:50</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Högt upp i tallöverståndare.</t>
+          <t>10:41</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1575,7 +1575,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123987786</v>
+        <v>123989116</v>
       </c>
       <c r="B10" t="n">
         <v>57529</v>
@@ -1609,21 +1609,26 @@
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>gammalt bo</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Rangelbäcken, Rangelbäcken, Vstm</t>
+          <t>Lilla Bergtjärnen, Lilla Bergtjärnen, Vstm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>480379</v>
+        <v>480299</v>
       </c>
       <c r="R10" t="n">
-        <v>6596690</v>
+        <v>6596637</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1655,7 +1660,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>08:58</t>
+          <t>09:41</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1665,12 +1670,12 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>08:58</t>
+          <t>09:41</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Bohål i tallöverståndare passande för pärluggla.</t>
+          <t>På jakt efter hästmyror i grövre gran.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1697,14 +1702,14 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123988025</v>
+        <v>123987555</v>
       </c>
       <c r="B11" t="n">
         <v>57513</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
+          <t>Behöver inte valideras</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1742,7 +1747,7 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>obs i häcktid, lämplig biotop</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
@@ -1751,10 +1756,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>480363</v>
+        <v>480411</v>
       </c>
       <c r="R11" t="n">
-        <v>6596775</v>
+        <v>6596690</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1786,7 +1791,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>09:05</t>
+          <t>08:44</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1796,12 +1801,12 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>09:05</t>
+          <t>08:44</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Födosökande på gran.</t>
+          <t>Ringbarkning i äldre tall.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1828,14 +1833,14 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123987592</v>
+        <v>123987670</v>
       </c>
       <c r="B12" t="n">
-        <v>57666</v>
+        <v>57513</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
+          <t>Behöver inte valideras</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1844,26 +1849,26 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -1871,14 +1876,9 @@
           <t>adult</t>
         </is>
       </c>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t>i par</t>
-        </is>
-      </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>par i lämplig häckbiotop</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
@@ -1887,10 +1887,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>480404</v>
+        <v>480411</v>
       </c>
       <c r="R12" t="n">
-        <v>6596699</v>
+        <v>6596749</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1922,7 +1922,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>08:46</t>
+          <t>08:51</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1932,7 +1932,12 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>08:46</t>
+          <t>08:51</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Ringbarkning i tallöverståndare.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1959,10 +1964,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>123989672</v>
+        <v>123988025</v>
       </c>
       <c r="B13" t="n">
-        <v>56722</v>
+        <v>57513</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1971,53 +1976,52 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100138</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K13" t="inlineStr">
         <is>
           <t>adult</t>
         </is>
       </c>
-      <c r="L13" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>obs i häcktid, lämplig biotop</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Stora Bergtjärnen, Stora Bergtjärnen, Vstm</t>
+          <t>Rangelbäcken, Rangelbäcken, Vstm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>480384</v>
+        <v>480363</v>
       </c>
       <c r="R13" t="n">
-        <v>6596389</v>
+        <v>6596775</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2049,7 +2053,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>09:51</t>
+          <t>09:05</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2059,7 +2063,12 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>09:51</t>
+          <t>09:05</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Födosökande på gran.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2086,14 +2095,14 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>123987555</v>
+        <v>123987592</v>
       </c>
       <c r="B14" t="n">
-        <v>57513</v>
+        <v>57666</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Behöver inte valideras</t>
+          <t>Godkänd baserat på observatörens uppgifter</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2102,26 +2111,26 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -2129,9 +2138,14 @@
           <t>adult</t>
         </is>
       </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>i par</t>
+        </is>
+      </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>par i lämplig häckbiotop</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
@@ -2140,10 +2154,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>480411</v>
+        <v>480404</v>
       </c>
       <c r="R14" t="n">
-        <v>6596690</v>
+        <v>6596699</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2175,7 +2189,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>08:44</t>
+          <t>08:46</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2185,12 +2199,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>08:44</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Ringbarkning i äldre tall.</t>
+          <t>08:46</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2217,37 +2226,37 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>123989116</v>
+        <v>123989693</v>
       </c>
       <c r="B15" t="n">
-        <v>57529</v>
+        <v>56722</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
+          <t>Behöver inte valideras</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100049</v>
+        <v>100138</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2258,19 +2267,19 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Lilla Bergtjärnen, Lilla Bergtjärnen, Vstm</t>
+          <t>Stora Bergtjärnen, Stora Bergtjärnen, Vstm</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>480299</v>
+        <v>480384</v>
       </c>
       <c r="R15" t="n">
-        <v>6596637</v>
+        <v>6596389</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2302,7 +2311,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>09:41</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2312,12 +2321,12 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>09:41</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>På jakt efter hästmyror i grövre gran.</t>
+          <t>Badgrop.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2344,14 +2353,14 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>123987670</v>
+        <v>123987786</v>
       </c>
       <c r="B16" t="n">
-        <v>57513</v>
+        <v>57529</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Behöver inte valideras</t>
+          <t>Godkänd baserat på observatörens uppgifter</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2360,16 +2369,16 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -2377,19 +2386,10 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K16" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
+      <c r="I16" t="inlineStr"/>
       <c r="M16" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>gammalt bo</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
@@ -2398,10 +2398,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>480411</v>
+        <v>480379</v>
       </c>
       <c r="R16" t="n">
-        <v>6596749</v>
+        <v>6596690</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2433,7 +2433,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>08:51</t>
+          <t>08:58</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2443,12 +2443,12 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>08:51</t>
+          <t>08:58</t>
         </is>
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Ringbarkning i tallöverståndare.</t>
+          <t>Bohål i tallöverståndare passande för pärluggla.</t>
         </is>
       </c>
       <c r="AD16" t="b">

--- a/artfynd/A 39826-2020 artfynd.xlsx
+++ b/artfynd/A 39826-2020 artfynd.xlsx
@@ -1234,7 +1234,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123988405</v>
+        <v>123987634</v>
       </c>
       <c r="B7" t="n">
         <v>78810</v>
@@ -1274,10 +1274,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>480313</v>
+        <v>480394</v>
       </c>
       <c r="R7" t="n">
-        <v>6596806</v>
+        <v>6596739</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1309,7 +1309,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>09:18</t>
+          <t>08:50</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1319,7 +1319,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>09:18</t>
+          <t>08:50</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Högt upp i tallöverståndare.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1346,10 +1351,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123987634</v>
+        <v>123991709</v>
       </c>
       <c r="B8" t="n">
-        <v>78810</v>
+        <v>79428</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1362,34 +1367,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Rangelbäcken, Rangelbäcken, Vstm</t>
+          <t>Stora Bergtjärnen, Stora Bergtjärnen, Vstm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>480394</v>
+        <v>480553</v>
       </c>
       <c r="R8" t="n">
-        <v>6596739</v>
+        <v>6596500</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1421,7 +1426,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>08:50</t>
+          <t>10:41</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1431,12 +1436,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>08:50</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Högt upp i tallöverståndare.</t>
+          <t>10:41</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1463,10 +1463,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123991709</v>
+        <v>123988405</v>
       </c>
       <c r="B9" t="n">
-        <v>79428</v>
+        <v>78810</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1479,34 +1479,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Stora Bergtjärnen, Stora Bergtjärnen, Vstm</t>
+          <t>Rangelbäcken, Rangelbäcken, Vstm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>480553</v>
+        <v>480313</v>
       </c>
       <c r="R9" t="n">
-        <v>6596500</v>
+        <v>6596806</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1538,7 +1538,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>10:41</t>
+          <t>09:18</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1548,7 +1548,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>10:41</t>
+          <t>09:18</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1575,7 +1575,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123989116</v>
+        <v>123987786</v>
       </c>
       <c r="B10" t="n">
         <v>57529</v>
@@ -1609,26 +1609,21 @@
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>gammalt bo</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Lilla Bergtjärnen, Lilla Bergtjärnen, Vstm</t>
+          <t>Rangelbäcken, Rangelbäcken, Vstm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>480299</v>
+        <v>480379</v>
       </c>
       <c r="R10" t="n">
-        <v>6596637</v>
+        <v>6596690</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1660,7 +1655,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>09:41</t>
+          <t>08:58</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1670,12 +1665,12 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>09:41</t>
+          <t>08:58</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>På jakt efter hästmyror i grövre gran.</t>
+          <t>Bohål i tallöverståndare passande för pärluggla.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1833,14 +1828,14 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123987670</v>
+        <v>123988025</v>
       </c>
       <c r="B12" t="n">
         <v>57513</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Behöver inte valideras</t>
+          <t>Godkänd baserat på observatörens uppgifter</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1878,7 +1873,7 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>obs i häcktid, lämplig biotop</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
@@ -1887,10 +1882,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>480411</v>
+        <v>480363</v>
       </c>
       <c r="R12" t="n">
-        <v>6596749</v>
+        <v>6596775</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1922,7 +1917,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>08:51</t>
+          <t>09:05</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1932,12 +1927,12 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>08:51</t>
+          <t>09:05</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Ringbarkning i tallöverståndare.</t>
+          <t>Födosökande på gran.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1964,10 +1959,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>123988025</v>
+        <v>123987592</v>
       </c>
       <c r="B13" t="n">
-        <v>57513</v>
+        <v>57666</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1980,26 +1975,26 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -2007,9 +2002,14 @@
           <t>adult</t>
         </is>
       </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>i par</t>
+        </is>
+      </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>obs i häcktid, lämplig biotop</t>
+          <t>par i lämplig häckbiotop</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
@@ -2018,10 +2018,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>480363</v>
+        <v>480404</v>
       </c>
       <c r="R13" t="n">
-        <v>6596775</v>
+        <v>6596699</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2053,7 +2053,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>09:05</t>
+          <t>08:46</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2063,12 +2063,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>09:05</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Födosökande på gran.</t>
+          <t>08:46</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2095,14 +2090,14 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>123987592</v>
+        <v>123987670</v>
       </c>
       <c r="B14" t="n">
-        <v>57666</v>
+        <v>57513</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
+          <t>Behöver inte valideras</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2111,26 +2106,26 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -2138,14 +2133,9 @@
           <t>adult</t>
         </is>
       </c>
-      <c r="L14" t="inlineStr">
-        <is>
-          <t>i par</t>
-        </is>
-      </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>par i lämplig häckbiotop</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
@@ -2154,10 +2144,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>480404</v>
+        <v>480411</v>
       </c>
       <c r="R14" t="n">
-        <v>6596699</v>
+        <v>6596749</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2189,7 +2179,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>08:46</t>
+          <t>08:51</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2199,7 +2189,12 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>08:46</t>
+          <t>08:51</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Ringbarkning i tallöverståndare.</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2226,14 +2221,14 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>123989693</v>
+        <v>123989672</v>
       </c>
       <c r="B15" t="n">
         <v>56722</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Behöver inte valideras</t>
+          <t>Godkänd baserat på observatörens uppgifter</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2265,9 +2260,14 @@
           <t>adult</t>
         </is>
       </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
@@ -2311,7 +2311,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>09:51</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2321,12 +2321,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>09:52</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Badgrop.</t>
+          <t>09:51</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2353,7 +2348,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>123987786</v>
+        <v>123989116</v>
       </c>
       <c r="B16" t="n">
         <v>57529</v>
@@ -2387,21 +2382,26 @@
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>gammalt bo</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Rangelbäcken, Rangelbäcken, Vstm</t>
+          <t>Lilla Bergtjärnen, Lilla Bergtjärnen, Vstm</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>480379</v>
+        <v>480299</v>
       </c>
       <c r="R16" t="n">
-        <v>6596690</v>
+        <v>6596637</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2433,7 +2433,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>08:58</t>
+          <t>09:41</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2443,12 +2443,12 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>08:58</t>
+          <t>09:41</t>
         </is>
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Bohål i tallöverståndare passande för pärluggla.</t>
+          <t>På jakt efter hästmyror i grövre gran.</t>
         </is>
       </c>
       <c r="AD16" t="b">

--- a/artfynd/A 39826-2020 artfynd.xlsx
+++ b/artfynd/A 39826-2020 artfynd.xlsx
@@ -1234,7 +1234,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123987634</v>
+        <v>123988405</v>
       </c>
       <c r="B7" t="n">
         <v>78810</v>
@@ -1274,10 +1274,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>480394</v>
+        <v>480313</v>
       </c>
       <c r="R7" t="n">
-        <v>6596739</v>
+        <v>6596806</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1309,7 +1309,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>08:50</t>
+          <t>09:18</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1319,12 +1319,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>08:50</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Högt upp i tallöverståndare.</t>
+          <t>09:18</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1351,10 +1346,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123991709</v>
+        <v>123987634</v>
       </c>
       <c r="B8" t="n">
-        <v>79428</v>
+        <v>78810</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1367,34 +1362,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Stora Bergtjärnen, Stora Bergtjärnen, Vstm</t>
+          <t>Rangelbäcken, Rangelbäcken, Vstm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>480553</v>
+        <v>480394</v>
       </c>
       <c r="R8" t="n">
-        <v>6596500</v>
+        <v>6596739</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1426,7 +1421,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>10:41</t>
+          <t>08:50</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1436,7 +1431,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>10:41</t>
+          <t>08:50</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Högt upp i tallöverståndare.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1463,10 +1463,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123988405</v>
+        <v>123991709</v>
       </c>
       <c r="B9" t="n">
-        <v>78810</v>
+        <v>79428</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1479,34 +1479,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Rangelbäcken, Rangelbäcken, Vstm</t>
+          <t>Stora Bergtjärnen, Stora Bergtjärnen, Vstm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>480313</v>
+        <v>480553</v>
       </c>
       <c r="R9" t="n">
-        <v>6596806</v>
+        <v>6596500</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1538,7 +1538,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>09:18</t>
+          <t>10:41</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1548,7 +1548,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>09:18</t>
+          <t>10:41</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1697,14 +1697,14 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123987555</v>
+        <v>123989116</v>
       </c>
       <c r="B11" t="n">
-        <v>57513</v>
+        <v>57529</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Behöver inte valideras</t>
+          <t>Godkänd baserat på observatörens uppgifter</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1713,16 +1713,16 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1730,11 +1730,7 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="K11" t="inlineStr">
         <is>
           <t>adult</t>
@@ -1742,19 +1738,19 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Rangelbäcken, Rangelbäcken, Vstm</t>
+          <t>Lilla Bergtjärnen, Lilla Bergtjärnen, Vstm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>480411</v>
+        <v>480299</v>
       </c>
       <c r="R11" t="n">
-        <v>6596690</v>
+        <v>6596637</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1786,7 +1782,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>08:44</t>
+          <t>09:41</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1796,12 +1792,12 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>08:44</t>
+          <t>09:41</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Ringbarkning i äldre tall.</t>
+          <t>På jakt efter hästmyror i grövre gran.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1828,14 +1824,14 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123988025</v>
+        <v>123987555</v>
       </c>
       <c r="B12" t="n">
         <v>57513</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
+          <t>Behöver inte valideras</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1873,7 +1869,7 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>obs i häcktid, lämplig biotop</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
@@ -1882,10 +1878,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>480363</v>
+        <v>480411</v>
       </c>
       <c r="R12" t="n">
-        <v>6596775</v>
+        <v>6596690</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1917,7 +1913,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>09:05</t>
+          <t>08:44</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1927,12 +1923,12 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>09:05</t>
+          <t>08:44</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Födosökande på gran.</t>
+          <t>Ringbarkning i äldre tall.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2090,64 +2086,65 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>123987670</v>
+        <v>123989672</v>
       </c>
       <c r="B14" t="n">
-        <v>57513</v>
+        <v>56722</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Behöver inte valideras</t>
+          <t>Godkänd baserat på observatörens uppgifter</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>100138</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
       <c r="K14" t="inlineStr">
         <is>
           <t>adult</t>
         </is>
       </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Rangelbäcken, Rangelbäcken, Vstm</t>
+          <t>Stora Bergtjärnen, Stora Bergtjärnen, Vstm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>480411</v>
+        <v>480384</v>
       </c>
       <c r="R14" t="n">
-        <v>6596749</v>
+        <v>6596389</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2179,7 +2176,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>08:51</t>
+          <t>09:51</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2189,12 +2186,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>08:51</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Ringbarkning i tallöverståndare.</t>
+          <t>09:51</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2221,65 +2213,64 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>123989672</v>
+        <v>123987670</v>
       </c>
       <c r="B15" t="n">
-        <v>56722</v>
+        <v>57513</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
+          <t>Behöver inte valideras</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100138</v>
+        <v>100109</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K15" t="inlineStr">
         <is>
           <t>adult</t>
         </is>
       </c>
-      <c r="L15" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Stora Bergtjärnen, Stora Bergtjärnen, Vstm</t>
+          <t>Rangelbäcken, Rangelbäcken, Vstm</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>480384</v>
+        <v>480411</v>
       </c>
       <c r="R15" t="n">
-        <v>6596389</v>
+        <v>6596749</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2311,7 +2302,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>09:51</t>
+          <t>08:51</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2321,7 +2312,12 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>09:51</t>
+          <t>08:51</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Ringbarkning i tallöverståndare.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2348,10 +2344,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>123989116</v>
+        <v>123988025</v>
       </c>
       <c r="B16" t="n">
-        <v>57529</v>
+        <v>57513</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2364,16 +2360,16 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -2381,7 +2377,11 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I16" t="inlineStr"/>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K16" t="inlineStr">
         <is>
           <t>adult</t>
@@ -2389,19 +2389,19 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>obs i häcktid, lämplig biotop</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Lilla Bergtjärnen, Lilla Bergtjärnen, Vstm</t>
+          <t>Rangelbäcken, Rangelbäcken, Vstm</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>480299</v>
+        <v>480363</v>
       </c>
       <c r="R16" t="n">
-        <v>6596637</v>
+        <v>6596775</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2433,7 +2433,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>09:41</t>
+          <t>09:05</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2443,12 +2443,12 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>09:41</t>
+          <t>09:05</t>
         </is>
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>På jakt efter hästmyror i grövre gran.</t>
+          <t>Födosökande på gran.</t>
         </is>
       </c>
       <c r="AD16" t="b">

--- a/artfynd/A 39826-2020 artfynd.xlsx
+++ b/artfynd/A 39826-2020 artfynd.xlsx
@@ -1824,14 +1824,14 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123987555</v>
+        <v>123987592</v>
       </c>
       <c r="B12" t="n">
-        <v>57513</v>
+        <v>57666</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Behöver inte valideras</t>
+          <t>Godkänd baserat på observatörens uppgifter</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1840,26 +1840,26 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -1867,9 +1867,14 @@
           <t>adult</t>
         </is>
       </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>i par</t>
+        </is>
+      </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>par i lämplig häckbiotop</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
@@ -1878,10 +1883,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>480411</v>
+        <v>480404</v>
       </c>
       <c r="R12" t="n">
-        <v>6596690</v>
+        <v>6596699</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1913,7 +1918,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>08:44</t>
+          <t>08:46</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1923,12 +1928,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>08:44</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Ringbarkning i äldre tall.</t>
+          <t>08:46</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1955,14 +1955,14 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>123987592</v>
+        <v>123987555</v>
       </c>
       <c r="B13" t="n">
-        <v>57666</v>
+        <v>57513</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
+          <t>Behöver inte valideras</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1971,26 +1971,26 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -1998,14 +1998,9 @@
           <t>adult</t>
         </is>
       </c>
-      <c r="L13" t="inlineStr">
-        <is>
-          <t>i par</t>
-        </is>
-      </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>par i lämplig häckbiotop</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
@@ -2014,10 +2009,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>480404</v>
+        <v>480411</v>
       </c>
       <c r="R13" t="n">
-        <v>6596699</v>
+        <v>6596690</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2049,7 +2044,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>08:46</t>
+          <t>08:44</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2059,7 +2054,12 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>08:46</t>
+          <t>08:44</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Ringbarkning i äldre tall.</t>
         </is>
       </c>
       <c r="AD13" t="b">

--- a/artfynd/A 39826-2020 artfynd.xlsx
+++ b/artfynd/A 39826-2020 artfynd.xlsx
@@ -1234,10 +1234,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123988405</v>
+        <v>123991709</v>
       </c>
       <c r="B7" t="n">
-        <v>78810</v>
+        <v>79428</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1250,34 +1250,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Rangelbäcken, Rangelbäcken, Vstm</t>
+          <t>Stora Bergtjärnen, Stora Bergtjärnen, Vstm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>480313</v>
+        <v>480553</v>
       </c>
       <c r="R7" t="n">
-        <v>6596806</v>
+        <v>6596500</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1309,7 +1309,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>09:18</t>
+          <t>10:41</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1319,7 +1319,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>09:18</t>
+          <t>10:41</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1346,7 +1346,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123987634</v>
+        <v>123988405</v>
       </c>
       <c r="B8" t="n">
         <v>78810</v>
@@ -1386,10 +1386,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>480394</v>
+        <v>480313</v>
       </c>
       <c r="R8" t="n">
-        <v>6596739</v>
+        <v>6596806</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1421,7 +1421,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>08:50</t>
+          <t>09:18</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1431,12 +1431,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>08:50</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Högt upp i tallöverståndare.</t>
+          <t>09:18</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1463,10 +1458,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123991709</v>
+        <v>123987634</v>
       </c>
       <c r="B9" t="n">
-        <v>79428</v>
+        <v>78810</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1479,34 +1474,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Stora Bergtjärnen, Stora Bergtjärnen, Vstm</t>
+          <t>Rangelbäcken, Rangelbäcken, Vstm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>480553</v>
+        <v>480394</v>
       </c>
       <c r="R9" t="n">
-        <v>6596500</v>
+        <v>6596739</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1538,7 +1533,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>10:41</t>
+          <t>08:50</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1548,7 +1543,12 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>10:41</t>
+          <t>08:50</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Högt upp i tallöverståndare.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1575,14 +1575,14 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123987786</v>
+        <v>123987670</v>
       </c>
       <c r="B10" t="n">
-        <v>57529</v>
+        <v>57513</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
+          <t>Behöver inte valideras</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1591,16 +1591,16 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1608,10 +1608,19 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr"/>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>gammalt bo</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
@@ -1620,10 +1629,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>480379</v>
+        <v>480411</v>
       </c>
       <c r="R10" t="n">
-        <v>6596690</v>
+        <v>6596749</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1655,7 +1664,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>08:58</t>
+          <t>08:51</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1665,12 +1674,12 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>08:58</t>
+          <t>08:51</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Bohål i tallöverståndare passande för pärluggla.</t>
+          <t>Ringbarkning i tallöverståndare.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1824,10 +1833,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123987592</v>
+        <v>123987786</v>
       </c>
       <c r="B12" t="n">
-        <v>57666</v>
+        <v>57529</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1840,41 +1849,27 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>103021</v>
+        <v>100049</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t>i par</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="M12" t="inlineStr">
         <is>
-          <t>par i lämplig häckbiotop</t>
+          <t>gammalt bo</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
@@ -1883,10 +1878,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>480404</v>
+        <v>480379</v>
       </c>
       <c r="R12" t="n">
-        <v>6596699</v>
+        <v>6596690</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1918,7 +1913,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>08:46</t>
+          <t>08:58</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1928,7 +1923,12 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>08:46</t>
+          <t>08:58</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Bohål i tallöverståndare passande för pärluggla.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1955,14 +1955,14 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>123987555</v>
+        <v>123987592</v>
       </c>
       <c r="B13" t="n">
-        <v>57513</v>
+        <v>57666</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Behöver inte valideras</t>
+          <t>Godkänd baserat på observatörens uppgifter</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1971,26 +1971,26 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -1998,9 +1998,14 @@
           <t>adult</t>
         </is>
       </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>i par</t>
+        </is>
+      </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>par i lämplig häckbiotop</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
@@ -2009,10 +2014,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>480411</v>
+        <v>480404</v>
       </c>
       <c r="R13" t="n">
-        <v>6596690</v>
+        <v>6596699</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2044,7 +2049,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>08:44</t>
+          <t>08:46</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2054,12 +2059,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>08:44</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Ringbarkning i äldre tall.</t>
+          <t>08:46</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2213,14 +2213,14 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>123987670</v>
+        <v>123988025</v>
       </c>
       <c r="B15" t="n">
         <v>57513</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Behöver inte valideras</t>
+          <t>Godkänd baserat på observatörens uppgifter</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2258,7 +2258,7 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>obs i häcktid, lämplig biotop</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
@@ -2267,10 +2267,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>480411</v>
+        <v>480363</v>
       </c>
       <c r="R15" t="n">
-        <v>6596749</v>
+        <v>6596775</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2302,7 +2302,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>08:51</t>
+          <t>09:05</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2312,12 +2312,12 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>08:51</t>
+          <t>09:05</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Ringbarkning i tallöverståndare.</t>
+          <t>Födosökande på gran.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2344,14 +2344,14 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>123988025</v>
+        <v>123987555</v>
       </c>
       <c r="B16" t="n">
         <v>57513</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
+          <t>Behöver inte valideras</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2389,7 +2389,7 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>obs i häcktid, lämplig biotop</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
@@ -2398,10 +2398,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>480363</v>
+        <v>480411</v>
       </c>
       <c r="R16" t="n">
-        <v>6596775</v>
+        <v>6596690</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2433,7 +2433,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>09:05</t>
+          <t>08:44</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2443,12 +2443,12 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>09:05</t>
+          <t>08:44</t>
         </is>
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Födosökande på gran.</t>
+          <t>Ringbarkning i äldre tall.</t>
         </is>
       </c>
       <c r="AD16" t="b">

--- a/artfynd/A 39826-2020 artfynd.xlsx
+++ b/artfynd/A 39826-2020 artfynd.xlsx
@@ -1575,14 +1575,14 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123987670</v>
+        <v>123987592</v>
       </c>
       <c r="B10" t="n">
-        <v>57513</v>
+        <v>57666</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Behöver inte valideras</t>
+          <t>Godkänd baserat på observatörens uppgifter</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1591,26 +1591,26 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -1618,9 +1618,14 @@
           <t>adult</t>
         </is>
       </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>i par</t>
+        </is>
+      </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>par i lämplig häckbiotop</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
@@ -1629,10 +1634,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>480411</v>
+        <v>480404</v>
       </c>
       <c r="R10" t="n">
-        <v>6596749</v>
+        <v>6596699</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1664,7 +1669,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>08:51</t>
+          <t>08:46</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1674,12 +1679,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>08:51</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Ringbarkning i tallöverståndare.</t>
+          <t>08:46</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1706,14 +1706,14 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123989116</v>
+        <v>123987670</v>
       </c>
       <c r="B11" t="n">
-        <v>57529</v>
+        <v>57513</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
+          <t>Behöver inte valideras</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1722,16 +1722,16 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1739,7 +1739,11 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr"/>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K11" t="inlineStr">
         <is>
           <t>adult</t>
@@ -1747,19 +1751,19 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Lilla Bergtjärnen, Lilla Bergtjärnen, Vstm</t>
+          <t>Rangelbäcken, Rangelbäcken, Vstm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>480299</v>
+        <v>480411</v>
       </c>
       <c r="R11" t="n">
-        <v>6596637</v>
+        <v>6596749</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1791,7 +1795,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>09:41</t>
+          <t>08:51</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1801,12 +1805,12 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>09:41</t>
+          <t>08:51</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>På jakt efter hästmyror i grövre gran.</t>
+          <t>Ringbarkning i tallöverståndare.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1833,10 +1837,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123987786</v>
+        <v>123989672</v>
       </c>
       <c r="B12" t="n">
-        <v>57529</v>
+        <v>56722</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1845,43 +1849,53 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100049</v>
+        <v>100138</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>gammalt bo</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Rangelbäcken, Rangelbäcken, Vstm</t>
+          <t>Stora Bergtjärnen, Stora Bergtjärnen, Vstm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>480379</v>
+        <v>480384</v>
       </c>
       <c r="R12" t="n">
-        <v>6596690</v>
+        <v>6596389</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1913,7 +1927,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>08:58</t>
+          <t>09:51</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1923,12 +1937,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>08:58</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Bohål i tallöverståndare passande för pärluggla.</t>
+          <t>09:51</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1955,10 +1964,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>123987592</v>
+        <v>123988025</v>
       </c>
       <c r="B13" t="n">
-        <v>57666</v>
+        <v>57513</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1971,26 +1980,26 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -1998,14 +2007,9 @@
           <t>adult</t>
         </is>
       </c>
-      <c r="L13" t="inlineStr">
-        <is>
-          <t>i par</t>
-        </is>
-      </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>par i lämplig häckbiotop</t>
+          <t>obs i häcktid, lämplig biotop</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
@@ -2014,10 +2018,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>480404</v>
+        <v>480363</v>
       </c>
       <c r="R13" t="n">
-        <v>6596699</v>
+        <v>6596775</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2049,7 +2053,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>08:46</t>
+          <t>09:05</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2059,7 +2063,12 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>08:46</t>
+          <t>09:05</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Födosökande på gran.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2086,10 +2095,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>123989672</v>
+        <v>123989116</v>
       </c>
       <c r="B14" t="n">
-        <v>56722</v>
+        <v>57529</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2098,25 +2107,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100138</v>
+        <v>100049</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2125,26 +2134,21 @@
           <t>adult</t>
         </is>
       </c>
-      <c r="L14" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Stora Bergtjärnen, Stora Bergtjärnen, Vstm</t>
+          <t>Lilla Bergtjärnen, Lilla Bergtjärnen, Vstm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>480384</v>
+        <v>480299</v>
       </c>
       <c r="R14" t="n">
-        <v>6596389</v>
+        <v>6596637</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2176,7 +2180,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>09:51</t>
+          <t>09:41</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2186,7 +2190,12 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>09:51</t>
+          <t>09:41</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>På jakt efter hästmyror i grövre gran.</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2213,10 +2222,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>123988025</v>
+        <v>123987786</v>
       </c>
       <c r="B15" t="n">
-        <v>57513</v>
+        <v>57529</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2229,16 +2238,16 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -2246,19 +2255,10 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
+      <c r="I15" t="inlineStr"/>
       <c r="M15" t="inlineStr">
         <is>
-          <t>obs i häcktid, lämplig biotop</t>
+          <t>gammalt bo</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
@@ -2267,10 +2267,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>480363</v>
+        <v>480379</v>
       </c>
       <c r="R15" t="n">
-        <v>6596775</v>
+        <v>6596690</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2302,7 +2302,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>09:05</t>
+          <t>08:58</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2312,12 +2312,12 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>09:05</t>
+          <t>08:58</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Födosökande på gran.</t>
+          <t>Bohål i tallöverståndare passande för pärluggla.</t>
         </is>
       </c>
       <c r="AD15" t="b">

--- a/artfynd/A 39826-2020 artfynd.xlsx
+++ b/artfynd/A 39826-2020 artfynd.xlsx
@@ -1575,10 +1575,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123987592</v>
+        <v>123987786</v>
       </c>
       <c r="B10" t="n">
-        <v>57666</v>
+        <v>57529</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1591,41 +1591,27 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>103021</v>
+        <v>100049</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L10" t="inlineStr">
-        <is>
-          <t>i par</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="M10" t="inlineStr">
         <is>
-          <t>par i lämplig häckbiotop</t>
+          <t>gammalt bo</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
@@ -1634,10 +1620,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>480404</v>
+        <v>480379</v>
       </c>
       <c r="R10" t="n">
-        <v>6596699</v>
+        <v>6596690</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1669,7 +1655,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>08:46</t>
+          <t>08:58</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1679,7 +1665,12 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>08:46</t>
+          <t>08:58</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Bohål i tallöverståndare passande för pärluggla.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1706,7 +1697,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123987670</v>
+        <v>123987555</v>
       </c>
       <c r="B11" t="n">
         <v>57513</v>
@@ -1763,7 +1754,7 @@
         <v>480411</v>
       </c>
       <c r="R11" t="n">
-        <v>6596749</v>
+        <v>6596690</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1795,7 +1786,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>08:51</t>
+          <t>08:44</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1805,12 +1796,12 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>08:51</t>
+          <t>08:44</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Ringbarkning i tallöverståndare.</t>
+          <t>Ringbarkning i äldre tall.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1837,10 +1828,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123989672</v>
+        <v>123988025</v>
       </c>
       <c r="B12" t="n">
-        <v>56722</v>
+        <v>57513</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1849,53 +1840,52 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100138</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K12" t="inlineStr">
         <is>
           <t>adult</t>
         </is>
       </c>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>obs i häcktid, lämplig biotop</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Stora Bergtjärnen, Stora Bergtjärnen, Vstm</t>
+          <t>Rangelbäcken, Rangelbäcken, Vstm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>480384</v>
+        <v>480363</v>
       </c>
       <c r="R12" t="n">
-        <v>6596389</v>
+        <v>6596775</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1927,7 +1917,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>09:51</t>
+          <t>09:05</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1937,7 +1927,12 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>09:51</t>
+          <t>09:05</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Födosökande på gran.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1964,44 +1959,40 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>123988025</v>
+        <v>123989693</v>
       </c>
       <c r="B13" t="n">
-        <v>57513</v>
+        <v>56722</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
+          <t>Behöver inte valideras</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>100138</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
       <c r="K13" t="inlineStr">
         <is>
           <t>adult</t>
@@ -2009,19 +2000,19 @@
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>obs i häcktid, lämplig biotop</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Rangelbäcken, Rangelbäcken, Vstm</t>
+          <t>Stora Bergtjärnen, Stora Bergtjärnen, Vstm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>480363</v>
+        <v>480384</v>
       </c>
       <c r="R13" t="n">
-        <v>6596775</v>
+        <v>6596389</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2053,7 +2044,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>09:05</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2063,12 +2054,12 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>09:05</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Födosökande på gran.</t>
+          <t>Badgrop.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2095,14 +2086,14 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>123989116</v>
+        <v>123987670</v>
       </c>
       <c r="B14" t="n">
-        <v>57529</v>
+        <v>57513</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
+          <t>Behöver inte valideras</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2111,16 +2102,16 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -2128,7 +2119,11 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I14" t="inlineStr"/>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K14" t="inlineStr">
         <is>
           <t>adult</t>
@@ -2136,19 +2131,19 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Lilla Bergtjärnen, Lilla Bergtjärnen, Vstm</t>
+          <t>Rangelbäcken, Rangelbäcken, Vstm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>480299</v>
+        <v>480411</v>
       </c>
       <c r="R14" t="n">
-        <v>6596637</v>
+        <v>6596749</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2180,7 +2175,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>09:41</t>
+          <t>08:51</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2190,12 +2185,12 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>09:41</t>
+          <t>08:51</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>På jakt efter hästmyror i grövre gran.</t>
+          <t>Ringbarkning i tallöverståndare.</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2222,10 +2217,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>123987786</v>
+        <v>123987592</v>
       </c>
       <c r="B15" t="n">
-        <v>57529</v>
+        <v>57666</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2238,27 +2233,41 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100049</v>
+        <v>103021</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>i par</t>
+        </is>
+      </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>gammalt bo</t>
+          <t>par i lämplig häckbiotop</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
@@ -2267,10 +2276,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>480379</v>
+        <v>480404</v>
       </c>
       <c r="R15" t="n">
-        <v>6596690</v>
+        <v>6596699</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2302,7 +2311,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>08:58</t>
+          <t>08:46</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2312,12 +2321,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>08:58</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Bohål i tallöverståndare passande för pärluggla.</t>
+          <t>08:46</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2344,14 +2348,14 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>123987555</v>
+        <v>123989116</v>
       </c>
       <c r="B16" t="n">
-        <v>57513</v>
+        <v>57529</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Behöver inte valideras</t>
+          <t>Godkänd baserat på observatörens uppgifter</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2360,16 +2364,16 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -2377,11 +2381,7 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I16" t="inlineStr"/>
       <c r="K16" t="inlineStr">
         <is>
           <t>adult</t>
@@ -2389,19 +2389,19 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Rangelbäcken, Rangelbäcken, Vstm</t>
+          <t>Lilla Bergtjärnen, Lilla Bergtjärnen, Vstm</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>480411</v>
+        <v>480299</v>
       </c>
       <c r="R16" t="n">
-        <v>6596690</v>
+        <v>6596637</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2433,7 +2433,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>08:44</t>
+          <t>09:41</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2443,12 +2443,12 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>08:44</t>
+          <t>09:41</t>
         </is>
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Ringbarkning i äldre tall.</t>
+          <t>På jakt efter hästmyror i grövre gran.</t>
         </is>
       </c>
       <c r="AD16" t="b">

--- a/artfynd/A 39826-2020 artfynd.xlsx
+++ b/artfynd/A 39826-2020 artfynd.xlsx
@@ -1697,14 +1697,14 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123987555</v>
+        <v>123988025</v>
       </c>
       <c r="B11" t="n">
         <v>57513</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Behöver inte valideras</t>
+          <t>Godkänd baserat på observatörens uppgifter</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1742,7 +1742,7 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>obs i häcktid, lämplig biotop</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
@@ -1751,10 +1751,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>480411</v>
+        <v>480363</v>
       </c>
       <c r="R11" t="n">
-        <v>6596690</v>
+        <v>6596775</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1786,7 +1786,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>08:44</t>
+          <t>09:05</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1796,12 +1796,12 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>08:44</t>
+          <t>09:05</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Ringbarkning i äldre tall.</t>
+          <t>Födosökande på gran.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1828,14 +1828,14 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123988025</v>
+        <v>123987555</v>
       </c>
       <c r="B12" t="n">
         <v>57513</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
+          <t>Behöver inte valideras</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1873,7 +1873,7 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>obs i häcktid, lämplig biotop</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
@@ -1882,10 +1882,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>480363</v>
+        <v>480411</v>
       </c>
       <c r="R12" t="n">
-        <v>6596775</v>
+        <v>6596690</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1917,7 +1917,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>09:05</t>
+          <t>08:44</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1927,12 +1927,12 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>09:05</t>
+          <t>08:44</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Födosökande på gran.</t>
+          <t>Ringbarkning i äldre tall.</t>
         </is>
       </c>
       <c r="AD12" t="b">

--- a/artfynd/A 39826-2020 artfynd.xlsx
+++ b/artfynd/A 39826-2020 artfynd.xlsx
@@ -1575,7 +1575,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123987786</v>
+        <v>123989116</v>
       </c>
       <c r="B10" t="n">
         <v>57529</v>
@@ -1609,21 +1609,26 @@
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>gammalt bo</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Rangelbäcken, Rangelbäcken, Vstm</t>
+          <t>Lilla Bergtjärnen, Lilla Bergtjärnen, Vstm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>480379</v>
+        <v>480299</v>
       </c>
       <c r="R10" t="n">
-        <v>6596690</v>
+        <v>6596637</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1655,7 +1660,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>08:58</t>
+          <t>09:41</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1665,12 +1670,12 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>08:58</t>
+          <t>09:41</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Bohål i tallöverståndare passande för pärluggla.</t>
+          <t>På jakt efter hästmyror i grövre gran.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1697,10 +1702,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123988025</v>
+        <v>123987786</v>
       </c>
       <c r="B11" t="n">
-        <v>57513</v>
+        <v>57529</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1713,16 +1718,16 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1730,19 +1735,10 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="M11" t="inlineStr">
         <is>
-          <t>obs i häcktid, lämplig biotop</t>
+          <t>gammalt bo</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
@@ -1751,10 +1747,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>480363</v>
+        <v>480379</v>
       </c>
       <c r="R11" t="n">
-        <v>6596775</v>
+        <v>6596690</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1786,7 +1782,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>09:05</t>
+          <t>08:58</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1796,12 +1792,12 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>09:05</t>
+          <t>08:58</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Födosökande på gran.</t>
+          <t>Bohål i tallöverståndare passande för pärluggla.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -2217,10 +2213,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>123987592</v>
+        <v>123988025</v>
       </c>
       <c r="B15" t="n">
-        <v>57666</v>
+        <v>57513</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2233,26 +2229,26 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -2260,14 +2256,9 @@
           <t>adult</t>
         </is>
       </c>
-      <c r="L15" t="inlineStr">
-        <is>
-          <t>i par</t>
-        </is>
-      </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>par i lämplig häckbiotop</t>
+          <t>obs i häcktid, lämplig biotop</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
@@ -2276,10 +2267,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>480404</v>
+        <v>480363</v>
       </c>
       <c r="R15" t="n">
-        <v>6596699</v>
+        <v>6596775</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2311,7 +2302,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>08:46</t>
+          <t>09:05</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2321,7 +2312,12 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>08:46</t>
+          <t>09:05</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Födosökande på gran.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2348,10 +2344,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>123989116</v>
+        <v>123987592</v>
       </c>
       <c r="B16" t="n">
-        <v>57529</v>
+        <v>57666</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2364,44 +2360,53 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100049</v>
+        <v>103021</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="K16" t="inlineStr">
         <is>
           <t>adult</t>
         </is>
       </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>i par</t>
+        </is>
+      </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>par i lämplig häckbiotop</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Lilla Bergtjärnen, Lilla Bergtjärnen, Vstm</t>
+          <t>Rangelbäcken, Rangelbäcken, Vstm</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>480299</v>
+        <v>480404</v>
       </c>
       <c r="R16" t="n">
-        <v>6596637</v>
+        <v>6596699</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2433,7 +2438,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>09:41</t>
+          <t>08:46</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2443,12 +2448,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>09:41</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>På jakt efter hästmyror i grövre gran.</t>
+          <t>08:46</t>
         </is>
       </c>
       <c r="AD16" t="b">

--- a/artfynd/A 39826-2020 artfynd.xlsx
+++ b/artfynd/A 39826-2020 artfynd.xlsx
@@ -1575,14 +1575,14 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123989116</v>
+        <v>123987670</v>
       </c>
       <c r="B10" t="n">
-        <v>57529</v>
+        <v>57513</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
+          <t>Behöver inte valideras</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1591,16 +1591,16 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1608,7 +1608,11 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr"/>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K10" t="inlineStr">
         <is>
           <t>adult</t>
@@ -1616,19 +1620,19 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Lilla Bergtjärnen, Lilla Bergtjärnen, Vstm</t>
+          <t>Rangelbäcken, Rangelbäcken, Vstm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>480299</v>
+        <v>480411</v>
       </c>
       <c r="R10" t="n">
-        <v>6596637</v>
+        <v>6596749</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1660,7 +1664,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>09:41</t>
+          <t>08:51</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1670,12 +1674,12 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>09:41</t>
+          <t>08:51</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>På jakt efter hästmyror i grövre gran.</t>
+          <t>Ringbarkning i tallöverståndare.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1702,10 +1706,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123987786</v>
+        <v>123989672</v>
       </c>
       <c r="B11" t="n">
-        <v>57529</v>
+        <v>56722</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1714,43 +1718,53 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100049</v>
+        <v>100138</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>gammalt bo</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Rangelbäcken, Rangelbäcken, Vstm</t>
+          <t>Stora Bergtjärnen, Stora Bergtjärnen, Vstm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>480379</v>
+        <v>480384</v>
       </c>
       <c r="R11" t="n">
-        <v>6596690</v>
+        <v>6596389</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1782,7 +1796,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>08:58</t>
+          <t>09:51</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1792,12 +1806,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>08:58</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Bohål i tallöverståndare passande för pärluggla.</t>
+          <t>09:51</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1824,14 +1833,14 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123987555</v>
+        <v>123988025</v>
       </c>
       <c r="B12" t="n">
         <v>57513</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Behöver inte valideras</t>
+          <t>Godkänd baserat på observatörens uppgifter</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1869,7 +1878,7 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>obs i häcktid, lämplig biotop</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
@@ -1878,10 +1887,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>480411</v>
+        <v>480363</v>
       </c>
       <c r="R12" t="n">
-        <v>6596690</v>
+        <v>6596775</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1913,7 +1922,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>08:44</t>
+          <t>09:05</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1923,12 +1932,12 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>08:44</t>
+          <t>09:05</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Ringbarkning i äldre tall.</t>
+          <t>Födosökande på gran.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1955,37 +1964,37 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>123989693</v>
+        <v>123989116</v>
       </c>
       <c r="B13" t="n">
-        <v>56722</v>
+        <v>57529</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Behöver inte valideras</t>
+          <t>Godkänd baserat på observatörens uppgifter</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100138</v>
+        <v>100049</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1996,19 +2005,19 @@
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Stora Bergtjärnen, Stora Bergtjärnen, Vstm</t>
+          <t>Lilla Bergtjärnen, Lilla Bergtjärnen, Vstm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>480384</v>
+        <v>480299</v>
       </c>
       <c r="R13" t="n">
-        <v>6596389</v>
+        <v>6596637</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2040,7 +2049,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>09:41</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2050,12 +2059,12 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>09:41</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Badgrop.</t>
+          <t>På jakt efter hästmyror i grövre gran.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2082,7 +2091,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>123987670</v>
+        <v>123987555</v>
       </c>
       <c r="B14" t="n">
         <v>57513</v>
@@ -2139,7 +2148,7 @@
         <v>480411</v>
       </c>
       <c r="R14" t="n">
-        <v>6596749</v>
+        <v>6596690</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2171,7 +2180,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>08:51</t>
+          <t>08:44</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2181,12 +2190,12 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>08:51</t>
+          <t>08:44</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Ringbarkning i tallöverståndare.</t>
+          <t>Ringbarkning i äldre tall.</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2213,10 +2222,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>123988025</v>
+        <v>123987786</v>
       </c>
       <c r="B15" t="n">
-        <v>57513</v>
+        <v>57529</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2229,16 +2238,16 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -2246,19 +2255,10 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
+      <c r="I15" t="inlineStr"/>
       <c r="M15" t="inlineStr">
         <is>
-          <t>obs i häcktid, lämplig biotop</t>
+          <t>gammalt bo</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
@@ -2267,10 +2267,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>480363</v>
+        <v>480379</v>
       </c>
       <c r="R15" t="n">
-        <v>6596775</v>
+        <v>6596690</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2302,7 +2302,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>09:05</t>
+          <t>08:58</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2312,12 +2312,12 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>09:05</t>
+          <t>08:58</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Födosökande på gran.</t>
+          <t>Bohål i tallöverståndare passande för pärluggla.</t>
         </is>
       </c>
       <c r="AD15" t="b">

--- a/artfynd/A 39826-2020 artfynd.xlsx
+++ b/artfynd/A 39826-2020 artfynd.xlsx
@@ -1575,10 +1575,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123987670</v>
+        <v>123989693</v>
       </c>
       <c r="B10" t="n">
-        <v>57513</v>
+        <v>56722</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1587,32 +1587,28 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>100138</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="K10" t="inlineStr">
         <is>
           <t>adult</t>
@@ -1625,14 +1621,14 @@
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Rangelbäcken, Rangelbäcken, Vstm</t>
+          <t>Stora Bergtjärnen, Stora Bergtjärnen, Vstm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>480411</v>
+        <v>480384</v>
       </c>
       <c r="R10" t="n">
-        <v>6596749</v>
+        <v>6596389</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1664,7 +1660,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>08:51</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1674,12 +1670,12 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>08:51</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Ringbarkning i tallöverståndare.</t>
+          <t>Badgrop.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1706,10 +1702,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123989672</v>
+        <v>123987592</v>
       </c>
       <c r="B11" t="n">
-        <v>56722</v>
+        <v>57666</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1718,28 +1714,32 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100138</v>
+        <v>103021</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="K11" t="inlineStr">
         <is>
           <t>adult</t>
@@ -1747,24 +1747,24 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>hane</t>
+          <t>i par</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>par i lämplig häckbiotop</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Stora Bergtjärnen, Stora Bergtjärnen, Vstm</t>
+          <t>Rangelbäcken, Rangelbäcken, Vstm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>480384</v>
+        <v>480404</v>
       </c>
       <c r="R11" t="n">
-        <v>6596389</v>
+        <v>6596699</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1796,7 +1796,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>09:51</t>
+          <t>08:46</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1806,7 +1806,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>09:51</t>
+          <t>08:46</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1833,14 +1833,14 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123988025</v>
+        <v>123987670</v>
       </c>
       <c r="B12" t="n">
         <v>57513</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
+          <t>Behöver inte valideras</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1878,7 +1878,7 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>obs i häcktid, lämplig biotop</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
@@ -1887,10 +1887,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>480363</v>
+        <v>480411</v>
       </c>
       <c r="R12" t="n">
-        <v>6596775</v>
+        <v>6596749</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1922,7 +1922,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>09:05</t>
+          <t>08:51</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1932,12 +1932,12 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>09:05</t>
+          <t>08:51</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Födosökande på gran.</t>
+          <t>Ringbarkning i tallöverståndare.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1964,7 +1964,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>123989116</v>
+        <v>123987786</v>
       </c>
       <c r="B13" t="n">
         <v>57529</v>
@@ -1998,26 +1998,21 @@
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>gammalt bo</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Lilla Bergtjärnen, Lilla Bergtjärnen, Vstm</t>
+          <t>Rangelbäcken, Rangelbäcken, Vstm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>480299</v>
+        <v>480379</v>
       </c>
       <c r="R13" t="n">
-        <v>6596637</v>
+        <v>6596690</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2049,7 +2044,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>09:41</t>
+          <t>08:58</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2059,12 +2054,12 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>09:41</t>
+          <t>08:58</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>På jakt efter hästmyror i grövre gran.</t>
+          <t>Bohål i tallöverståndare passande för pärluggla.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2091,14 +2086,14 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>123987555</v>
+        <v>123989116</v>
       </c>
       <c r="B14" t="n">
-        <v>57513</v>
+        <v>57529</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Behöver inte valideras</t>
+          <t>Godkänd baserat på observatörens uppgifter</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2107,16 +2102,16 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -2124,11 +2119,7 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I14" t="inlineStr"/>
       <c r="K14" t="inlineStr">
         <is>
           <t>adult</t>
@@ -2136,19 +2127,19 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Rangelbäcken, Rangelbäcken, Vstm</t>
+          <t>Lilla Bergtjärnen, Lilla Bergtjärnen, Vstm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>480411</v>
+        <v>480299</v>
       </c>
       <c r="R14" t="n">
-        <v>6596690</v>
+        <v>6596637</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2180,7 +2171,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>08:44</t>
+          <t>09:41</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2190,12 +2181,12 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>08:44</t>
+          <t>09:41</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Ringbarkning i äldre tall.</t>
+          <t>På jakt efter hästmyror i grövre gran.</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2222,14 +2213,14 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>123987786</v>
+        <v>123987555</v>
       </c>
       <c r="B15" t="n">
-        <v>57529</v>
+        <v>57513</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
+          <t>Behöver inte valideras</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2238,16 +2229,16 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -2255,10 +2246,19 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I15" t="inlineStr"/>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>gammalt bo</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
@@ -2267,7 +2267,7 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>480379</v>
+        <v>480411</v>
       </c>
       <c r="R15" t="n">
         <v>6596690</v>
@@ -2302,7 +2302,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>08:58</t>
+          <t>08:44</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2312,12 +2312,12 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>08:58</t>
+          <t>08:44</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Bohål i tallöverståndare passande för pärluggla.</t>
+          <t>Ringbarkning i äldre tall.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2344,10 +2344,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>123987592</v>
+        <v>123988025</v>
       </c>
       <c r="B16" t="n">
-        <v>57666</v>
+        <v>57513</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2360,26 +2360,26 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -2387,14 +2387,9 @@
           <t>adult</t>
         </is>
       </c>
-      <c r="L16" t="inlineStr">
-        <is>
-          <t>i par</t>
-        </is>
-      </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>par i lämplig häckbiotop</t>
+          <t>obs i häcktid, lämplig biotop</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
@@ -2403,10 +2398,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>480404</v>
+        <v>480363</v>
       </c>
       <c r="R16" t="n">
-        <v>6596699</v>
+        <v>6596775</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2438,7 +2433,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>08:46</t>
+          <t>09:05</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2448,7 +2443,12 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>08:46</t>
+          <t>09:05</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Födosökande på gran.</t>
         </is>
       </c>
       <c r="AD16" t="b">
